--- a/source/marked/marked_LTRL Chapter I ver0.xlsx
+++ b/source/marked/marked_LTRL Chapter I ver0.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O636"/>
+  <dimension ref="A1:O679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>本文档仅供组内学习交流使用，严禁商用！严禁外传！</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -438,11 +438,7 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -461,7 +457,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>认领章节/分工具体内容及流程请见</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -480,11 +476,7 @@
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -503,7 +495,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">本章工序总认领人：拆分: Lanx; 机翻: Lanx; 人工翻译: tuche; 润色: ?; 校对: ?; 游击队:?									</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -524,7 +516,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tuche est</t>
+          <t>翻译须知及规范</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -545,7 +537,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Lanx专属行的底色为金色（屎黄色）</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -566,7 +558,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> tuche est</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -587,7 +579,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mecius</t>
+          <t>簪花落梅</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -608,7 +600,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Yancey（暂时前来查漏补缺，捡一些还没人做的来做，目前可能主要负责润色与校对，浅紫1）</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -629,7 +621,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【译者注释】</t>
+          <t>Mecius</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -650,7 +642,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>本章特殊规范（由各组自定义）：</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -671,7 +663,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>注：本章开始，1.0版本只做一次润色和校对，第二次放到2.0版本。</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -692,7 +684,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【二级标题原文】</t>
+          <t>《简明拉丁语》计划：本章为试验章，除去原文翻译外，还可对原文进行”简明化“，即用自己的话重述原文要点，进行大量删改。另起一行，不破坏原文翻译行。</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -711,11 +703,7 @@
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>【二级标题译文】</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -734,7 +722,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>序号43，页数11（拆分：1，Lanx）（机翻：1，Lanx）（人翻：？，？）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -753,11 +741,7 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -776,7 +760,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Vocabulary</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -797,7 +781,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>单词表</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -818,7 +802,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>单词表暂缓</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -839,7 +823,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【二级标题原文】</t>
+          <t>认领你的专属行颜色（保证文字和背景方便辨认，文字颜色也可更改，但注意不要与常用文字颜色重复，</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -860,7 +844,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【二级标题译文】</t>
+          <t>1. 词汇条目旁边的箭头表示在后面的词汇注释中还有其他有关此条目的重要信息</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -881,7 +865,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vocabulary Notes</t>
+          <t>如红色文字标记重点</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -900,11 +884,7 @@
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -923,7 +903,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>序号44，页数12（拆分：1，Lanx）（机翻：？，？）（人翻：2, 簪花落梅, tuche）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -942,11 +922,7 @@
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>）</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -965,7 +941,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>Vocabulary</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -986,7 +962,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>单词表</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1007,7 +983,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Vocabulary Notes</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1028,7 +1004,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>&gt;anima,animae f.has a physical meaning.the "breath"of the wind or of a human being.By extension,it may mean the breath of life,the force that gives an animate being life(life force).</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1049,7 +1025,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>具有物理意义，即风或人之“呼吸”。广义而言，它可能意味着生命的呼吸，赋予生命存在的力量（生命力）。用于指代人死后前往冥界的灵魂</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1070,7 +1046,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>）</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1091,7 +1067,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>anima is used of the part of a human being that departs from the dead body and journeys to another life in the underworld.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1112,7 +1088,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>（在拉丁语中，）anima被视为人体的一部分，（在人死亡后）离开身体，前往冥界继续生活。</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1133,7 +1109,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>anima是指一个人离开尸体，前往阴间另一个生命之旅的角色。</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1154,7 +1130,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>physical：实体/物质的；by extension：引申后/经过引申；</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1175,7 +1151,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>*并入上一行且翻译不准确</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1196,7 +1172,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>&gt;fama,famae f.derives from an Indo-European root that means"speak"(cf.Gk.phemi;Skt.bhash,speak).The word fama indicates primarily what is spoken publicly or by the people,and its basic meaning is"talk" or"rumor."</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1217,7 +1193,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>源自印欧语系的词根，意思是“说话”（cf.Gk.phemi；Skt.bhash，speak）。fama一词主要表示公开或人民所说的话，其基本含义是“谈话”或“谣言”</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1238,7 +1214,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>词根源于印欧语系，意指“说话” （不知道）该词汇指公开或者群体所说的话，本意为“谈话”或“谣言”</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1259,7 +1235,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>&gt;fama, famae (f.)源自印欧语词根*bha-，意为“说话”（对比希腊语phemi和梵语bhash，均意指“说话”）。该单词最初是指面向群众或公开的言论，故其基本含义为“话语”或“谣言”。</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1280,7 +1256,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>A fama often told becomes a"story,"and when it is passed down from generation to genera- tion,it becomes a"tradition."A person's fama is his or her"reputation"or"fame."This may be positive or negative.Finally,if the word is capitalized,Fama is the goddess Rumor.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1301,7 +1277,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>一个经常讲的fama变成了一个“故事”，当它代代相传时，它就变成了一种“传统”。一个人的fama是他或她的“声誉”或“名声”。这可能是积极的，也可能是消极的。最后，如果这个词被大写，法玛就是女神Rumor。</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1322,7 +1298,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>广为流传的“言论（fama）”会逐渐演变为“故事”。一个地方的“故事”代代相传，就逐渐流变、塑造、组成了当地的“传统（或传统风俗）”。一个人身上为他人所传道的话题（fama）也就成为了其自身或褒或贬的“声誉”。首字母大写的Fama即古罗马神话中传闻女神（或译作谣言女神）Rumor的另一个名字。</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1343,7 +1319,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>该词意义多变，常指“故事”，或指代代相传的“传统”；用于个人时，又指其或善或恶的“声誉”、“名声”。首字母大写又是女神Rumor，即希腊神话中的传闻女神俄萨,罗马人称她Fama(法玛)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1364,7 +1340,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>Fama就是女神Rumor/Fame指女神Rumor</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1385,7 +1361,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>&gt;deus,dei m.has certain common irregular forms in the plural.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1406,7 +1382,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>deus其复数形式中有常见的不规则形式</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1427,7 +1403,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>Deus拥有部分常见的不规则复数变格。</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1448,7 +1424,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>MEMORIZE THE FOLLOWING DECLENSION: Nom./Voc.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1469,7 +1445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>谨记以下变格：Nom./Voc.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1490,7 +1466,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Nom./Voc.    deus       dī</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1511,7 +1487,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1. An arrow next to a vocabulary entry indicates that there is additional important information about this entry in the</t>
+          <t xml:space="preserve">Gen.             deī     deōrum or deum  </t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1532,7 +1508,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> vocabulary notes</t>
+          <t>Dat.              deō        dīs</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1553,7 +1529,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Acc.             deurm    deōs</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -1574,7 +1550,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt;The noun dominus,domini m.is cognate with the Latin word for house(domus);that is,the two words dominus and domus are descended from the same linguistic root.The original meaning of dominus was "master of the house." </t>
+          <t xml:space="preserve">Abl.              deō        dīs </t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1593,11 +1569,7 @@
       <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> that follow.</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
@@ -1616,7 +1588,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>There is no vocative singular of deus.Other,less common forms of the nominative/vocative plural are dei and dit.A less common form of the dative/ablative plural is deīs.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -1637,7 +1609,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>deus没有主格单数。主格/呼格复数的其他不太常见的形式是dei和dit。与格/属格复数的一种不太常见形式是deīs。</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -1658,7 +1630,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>1. An arrow next to a vocabulary entry indicates that there is additional important information about this entry in the</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -1679,7 +1651,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt;consilium,consilii n.may mean the act of deliberating about something(deliberation),or it may mean the "plan"or"intention"that results from deliberating.It may also mean the capacity to deliberate(judgment) Finally,it may refer to a group of people who deliberate,a"council." </t>
+          <t xml:space="preserve"> vocabulary notes</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -1700,7 +1672,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>较少常见的形式为</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -1721,7 +1693,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>&gt;ferrum,ferri n.means "iron."By the rhetorical device metonymy (change of name)it also means “sword”-that is,something made of iron.</t>
+          <t xml:space="preserve">&gt;The noun dominus,domini m.is cognate with the Latin word for house(domus);that is,the two words dominus and domus are descended from the same linguistic root.The original meaning of dominus was "master of the house." </t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -1742,7 +1714,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> that follow.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -1763,7 +1735,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>1.词旁箭头表示</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -1784,7 +1756,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Prepositions</t>
+          <t>that is：即</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -1805,7 +1777,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>该词与拉丁语的房屋（domus）同源，其本义为“屋子的主人”。</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -1826,7 +1798,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A preposition (praepono,place before)is a word placed before a noun or pronoun to show its relation to another word in the sentence.</t>
+          <t xml:space="preserve">&gt;consilium,consilii n.may mean the act of deliberating about something(deliberation),or it may mean the "plan"or"intention"that results from deliberating.It may also mean the capacity to deliberate(judgment) Finally,it may refer to a group of people who deliberate,a"council." </t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -1847,7 +1819,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>该词可指反复思考这一行为本身，也可指反复思考所得的结果——计划，亦可指反复思考的能力（判断力），还可指代一群负责反复思考的人，也就是“委员会”。</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -1868,7 +1840,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>&gt;ferrum,ferri n.means "iron."By the rhetorical device metonymy (change of name)it also means “sword”-that is,something made of iron.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -1889,7 +1861,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>该词本义为“铁”，也可用于借代“剑”。</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1910,7 +1882,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>rhetorical device metonymy：修辞手法 转喻；“由铁制成的剑”</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1931,7 +1903,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>Prepositions</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -1952,7 +1924,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>介词</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1973,7 +1945,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> A preposition (praepono,place before)is a word placed before a noun or pronoun to show its relation to another word in the sentence.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1994,7 +1966,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Prepositions that take the accusative emphasize the idea of motion toward,into,around,and through.</t>
+          <t>介词 (praepono,置于前)是一类置于名词或代词之前，用于表达其与句中其余成分间关系的词。</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2015,7 +1987,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>介词 (praepositio，源自praepono，意为“前置”)是一种位于名词或代词前，表达自身与其他句子成分关系的词类。</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2036,7 +2008,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>The preposition and the noun or pronoun together are called a "prepositional phrase."In Latin,prepositions are most often followed by one of two cases,the accusative or the ablative.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -2057,7 +2029,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>介词与名词或代词一同构成介词短语。在拉丁语中，介词后的单词绝大多数情况下是宾格或离格。</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -2078,7 +2050,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Prepositions that require a noun in the accusative case are said to"take the accusative"and are marked in the vocabulary entry by the notation (prep.+acc.).</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2099,7 +2071,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Prepositions that take the ablative indicate one of the three functions of the ablative(separation,association/ instrument,location).</t>
+          <t>注释</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2120,7 +2092,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>若一个介词的后置单词为宾格，那么我们说这个介词“*后接宾格”，在单词表中标记为(praep.+acc.)（即praepositio+accusativus (casus)）</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -2141,7 +2113,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Prepositions that take the accusative emphasize the idea of motion toward,into,around,and through.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2162,7 +2134,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>有其他重要信息</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2183,7 +2155,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Prepositions that require a noun in the ablative case are simi- larly said to"take the ablative"and are marked by the notation (prep.+abl.).</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -2204,7 +2176,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt;The prepositions a/ab,e/ex,and de all require a noun in the ablative case and express separation (from).	</t>
+          <t>&gt;anima, animae (f.)可指代实体概念，即“风或人的‘呼吸’”。*后来可能经过进一步的引申，而拥有了“生命的呼吸、赋予生命延续的力量（即生命力）”的意味。</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2225,7 +2197,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>类似的，若一个介词的后置单词为离格，那么我们说这个介词“*后跟离格”，标记为(praep.+abl.)（即praepositio+ablativus (casus)）</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -2246,7 +2218,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Prepositions that take the ablative indicate one of the three functions of the ablative(separation,association/ instrument,location).</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -2267,7 +2239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>取离格的介词则暗含着离格的三个功能（表分离、表连携或表手段、表位置）之一。</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -2288,7 +2260,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>{*by extension翻译为“引申；再则”}</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -2309,7 +2281,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>一些介词既可以取宾格也可以取离格，它们的含义也随之改变。</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -2330,7 +2302,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>一般而言，若动词表示动作，则介词后接宾格；若动词表示静止，则介词后跟夺格。</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -2351,7 +2323,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>&gt;ab is used before words beginning with vowels or h-.Both a and ab are used before words beginning with consonants,but a is more frequent.</t>
+          <t xml:space="preserve">&gt;The prepositions a/ab,e/ex,and de all require a noun in the ablative case and express separation (from).	</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -2372,7 +2344,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>介词a/ab,e/ex,和de 均取离格，表示自某处分离</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -2393,7 +2365,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>介词a/ab,e/ex,和de 均后跟离格，表示自某处分离</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -2414,7 +2386,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt;ex is used before words beginning with vowels or h-.Both e and ex are used before words beginning with consonants,but ex is more frequent.		</t>
+          <t xml:space="preserve">However,they have distinct differences in meaning.a/ab expresses motion away from a place;e/exex- presses motion out from a place;de expresses motion down from a place.These differences in meaning are illustrated in the diagram that follows.		</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -2435,7 +2407,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>不过它们的含义清晰有别：a/ab表示“远离”，e/ex表示“出离”，de则表示“（自上而）下离”。下图形象地展现了它们之间的区别。</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -2456,7 +2428,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>不过它们的含义清晰有别：a/ab表示“远离”，e/ex表示“从内而外的离开”，而de则表示一种“自上而下的运动”。下图形象地展现了彼此之间的区别。</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -2477,7 +2449,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>离，出，落</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -2498,7 +2470,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>&gt;ab is used before words beginning with vowels or h-.Both a and ab are used before words beginning with consonants,but a is more frequent.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -2519,7 +2491,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>&gt;in may take either the accusative or the ablative case.When it takes the accusative,it means "into"or "onto."By extension of this meaning it may also mean"against,"especially when the noun in the accusative case refers to a person or people.</t>
+          <t>以元音或h开头的单词前仅可使用ab，其余单词则两者皆可，不过a更常用。</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -2540,7 +2512,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>以元音或辅音h开头的单词之前仅能使用ab，其余则两者皆可，但a更常见。</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -2561,7 +2533,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>When it takes the ablative case,it expresses location and means ei- ther"in"or"on."These differences in meaning are illustrated in the diagram that follows</t>
+          <t xml:space="preserve">&gt;ex is used before words beginning with vowels or h-.Both e and ex are used before words beginning with consonants,but ex is more frequent.		</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -2582,7 +2554,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>以元音或h开头的单词前仅可使用ex，其余单词则两者皆可，不过ex更常用。</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -2603,7 +2575,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>以元音或辅音h开头的单词之前仅能使用ex，其余则两者皆可，但ex更常见。</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -2624,7 +2596,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>deus没有单数呼格，其他不太常见的有：dei和</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -2645,7 +2617,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>ad取宾格，表示前往。下图将展现ad与in取宾格时的区别。</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -2666,7 +2638,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Figure 2. Prepositions</t>
+          <t>&gt;in may take either the accusative or the ablative case.When it takes the accusative,it means "into"or "onto."By extension of this meaning it may also mean"against,"especially when the noun in the accusative case refers to a person or people.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -2687,7 +2659,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>in既可以取宾格也可以取离格。取宾格时，in表示“进入”或“登上”，它有着一个引申义“对抗”，在对象是“人”时尤为常见。</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -2706,11 +2678,7 @@
       <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&gt; et is a coordinating conjunction. This means that it connects only parallel or grammatically balanced words, phrases, or clauses. When two nouns are connected, they must be in the same case: for example, nautārum et agricolarum (of the sailors and of the farmers (genitive]). </t>
-        </is>
-      </c>
+      <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
@@ -2729,7 +2697,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>When it takes the ablative case,it expresses location and means ei- ther"in"or"on."These differences in meaning are illustrated in the diagram that follows</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -2750,7 +2718,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>取离格时，它表位置，意为“于其中”或“于其上”。下图也将展现这一区别</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -2771,7 +2739,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>后接离格时，表示（中心语所处的）位置，意为“处其中”或“在其上”。下图将展现它们的区别</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -2790,11 +2758,7 @@
       <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
@@ -2811,11 +2775,7 @@
       <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To emphasize the strict balance of elements that are to be ioined in Latin, et is often used to mark each element: et nautārum et agricolārum, "both of the sailors and of the farmers." </t>
-        </is>
-      </c>
+      <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
@@ -2834,7 +2794,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>序号45，页数13（拆分：1，Lanx）（机翻：1，Lanx）（人翻：？，？）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -2853,11 +2813,7 @@
       <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
@@ -2876,7 +2832,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>图略</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -2895,11 +2851,7 @@
       <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
@@ -2918,7 +2870,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Figure 2. Prepositions</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -2939,7 +2891,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>图2.介词</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -2960,7 +2912,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t xml:space="preserve">&gt; et is a coordinating conjunction. This means that it connects only parallel or grammatically balanced words, phrases, or clauses. When two nouns are connected, they must be in the same case: for example, nautārum et agricolarum (of the sailors and of the farmers (genitive]). </t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -2981,7 +2933,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>et是个并列连词，它仅用于连接同类或语法上一致的单词、短语、或从句。它连接的两个的名词需同格：例如，nautārum et agricolarum（水手们的与农民们的）</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -3002,7 +2954,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Parts of speech other than nouns may also be connected by et. For example, in the phrases "tall and snow-covered," "he sings and he dances," "in Italy and in Gaul," et could again be used to connect two adjectives, two verb phrases, or two prepositional phrases.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -3023,7 +2975,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt;-que is an enclitic conjunction. The word enclitic is derived from the Greek verb enklino (lean on), and an enclitic leans on or is directly attached to the word preceding it. </t>
+          <t xml:space="preserve">名词以外的词性也可以通过 et 连接。例如，在短语“高大而白雪覆盖”，“他唱歌，他跳舞”，“在意大利和高卢”中，et再次可用于连接两个形容词，两个动词短语或两个介词短语。 </t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -3044,7 +2996,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>et也可用于连接其余词性的成分。例如，短语“高大且被白雪覆盖”“他唱歌又跳舞”“在意大利和高卢”中，et依次连接了两个形容词，两个动词，以及两个介词短语。</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -3065,7 +3017,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">dit </t>
+          <t xml:space="preserve">To emphasize the strict balance of elements that are to be ioined in Latin, et is often used to mark each element: et nautārum et agricolārum, "both of the sailors and of the farmers." </t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -3086,7 +3038,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>为了强调拉丁语中要加入的元素的严格平衡，et通常用于标记每个元素：et nautārum et agricolārum，“水手和农民”。</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -3107,7 +3059,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>为了强调拉丁语中元素间严格的平衡，et常用于标记出并列的元素：nautārum et agricolārum，“水手与农民”</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -3128,7 +3080,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>It is convenient to translate the first et with the English word "both." When such a parallel series is longer than two (et nautārum et agricolārum et poetārum), the first et is not translated (of the sailors and of the farmers and of the poets).</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -3149,7 +3101,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>用英文单词“both”翻译第一个 et 很方便。当这样的平行序列超过两个（et nautārum et agricolārum et poetārum）时，第一个 et 不会被翻译（水手、农民和诗人）</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -3170,7 +3122,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>这句话对讲汉语的人来说意义不大，我先跳过了</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -3191,7 +3143,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>et……et可译为both……and，拉丁语中et……et这样的结构可以一直并列下去，如et nautārum et agricolārum et poetārum，汉语在翻译时一般不会翻译第一个et：水手们、农民们与诗人们的。</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -3212,7 +3164,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>-que is used in place of the first et in the phrase et . .. et . .. by certain prose stylists (the historians Livy, Sallust, and Tacitus) and by many poets. Caesar and Cicero never use -que...et .. The use of -que... -que... is found only in poetry and occasionally in the historians</t>
+          <t xml:space="preserve">et may also be used as an adverb that usually qualifies a single word (noun, verb, adjective): et vir, "even the man." "the man also." </t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -3233,7 +3185,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>ET也可以用作副词，通常限定单个单词（名词，动词，形容词）：et vir，“甚至男人”。“那人也是。”</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -3254,7 +3206,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>et也可作副词，常用于限定单个单词（名词、动词、形容词）：et vir，“甚至那个男人”“那个男人也是”。</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -3275,7 +3227,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t xml:space="preserve">&gt;-que is an enclitic conjunction. The word enclitic is derived from the Greek verb enklino (lean on), and an enclitic leans on or is directly attached to the word preceding it. </t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -3296,7 +3248,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivatives and Cognates </t>
+          <t>&gt;-que是一个斜合相。enclitic这个词来源于希腊语动词enklino（lean on），enclitic依靠或直接附加到它前面的单词上。</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -3317,7 +3269,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">dit </t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -3338,7 +3290,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Many words in English are derived from Latin words; that is, they descend directly from words in Latin. Such words are called derivatives. For example, the English word "counsel" is a derivative of the Latin word cônsilium.A</t>
+          <t>The hyphen before que indicates that it cannot stand alone as a separate word. -que is attached to the second element of a closely related pair, whose elements are often opposite or complementary.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -3359,7 +3311,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>que 前面的连字符表示它不能作为一个单独的单词独立存在。-que 附加到密切相关的对的第二个元素上，其元素通常是相反或互补的</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -3380,7 +3332,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>-que 前面的连字符表明它不能独立使用，只能附加在一对元素的第二个单词上，这对元素彼此间联系密切，通常相反或互补。</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -3401,7 +3353,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t xml:space="preserve"> -que should be translated "and" before the word to which it is attached: for example, vir feminaque (husband and wife [subjects]). Like et, -que may connect grammatical elements other than nouns.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -3422,7 +3374,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>-que应该在它所附的单词之前翻译为“and”：例如，vir feminaque（丈夫和妻子[主语]）。像et一样，-que可以连接名词以外的语法元素</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -3443,7 +3395,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>作为复数主格、呼格， deīs作为复数与格、离格</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -3464,7 +3416,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>-que is used in place of the first et in the phrase et . .. et . .. by certain prose stylists (the historians Livy, Sallust, and Tacitus) and by many poets. Caesar and Cicero never use -que...et .. The use of -que... -que... is found only in poetry and occasionally in the historians</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -3485,7 +3437,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>-que 用于代替短语 et 中的第一个 et。..等等。..由某些散文风格家（历史学家李维、萨卢斯特和塔西佗）和许多诗人。凯撒和西塞罗从不使用-que...等等..-que... -que...只在诗歌中找到，偶尔在历史学家中发现</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -3506,7 +3458,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>许多诗人与一些文体家（历史学家李维、萨卢斯特和塔西佗）会用-que来代替短语“et ... et ...”中的第一个et，凯撒和西塞罗则从不这样写。短语“-que... -que...”通常只在诗歌中出现，历史学家偶尔也会用。</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -3527,7 +3479,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>序号46，页数14（拆分：1，Lanx）（机翻：？，？）（人翻：？，？）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -3546,11 +3498,7 @@
       <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
@@ -3569,7 +3517,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t xml:space="preserve">Derivatives and Cognates </t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -3590,7 +3538,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>派生词和同源词</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -3611,7 +3559,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Many words in English are derived from Latin words; that is, they descend directly from words in Latin. Such words are called derivatives. For example, the English word "counsel" is a derivative of the Latin word cônsilium.A</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -3632,7 +3580,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>英语中的许多单词都源自拉丁语单词;也就是说，它们直接来自拉丁语中的单词。这样的词被称为衍生词。例如，英语单词“counsel”是拉丁词cônsilium的衍生词。一个</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -3653,7 +3601,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>许多英语单词派生自拉丁语单词，也就是说，它们直接由拉丁语单词变来，我们称这些词为派生词。例如，英语单词“counsel”便由拉丁语单词“cônsilium”派生而来。</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -3674,7 +3622,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> In many instances, the differences in sound and spelling between an English word and its Latin parent are not significant enough to obscure the fact that the two words are related. </t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -3695,7 +3643,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>在许多情况下，英语单词与其拉丁语父词之间的发音和拼写差异不足以掩盖这两个单词相关的事实。</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -3716,7 +3664,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Deus没有单数呼格。*另外，其复数主格与呼格有一种不太常见的形式deī和diī；复数与格和离格不太常见的形式为deīs。</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -3737,7 +3685,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>{*按照英文原文的句式结构翻译的}</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -3758,7 +3706,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>一般而言，英语派生词与其拉丁语母词往往在拼写或读音上相近或相似。</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -3779,7 +3727,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Some English derivatives descend from the roots of Latin words. A root is the basic element or ultimate stem of a word that carries its meaning and from which many other words are made by the addition of prefixes and suffixes.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -3800,7 +3748,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>一些英语衍生词源自拉丁词的词根。词根是具有其含义的单词的基本元素或最终词干，并且通过添加前缀和后缀来制作许多其他单词</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -3821,7 +3769,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>&gt;名词</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -3842,7 +3790,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">When an English and a Latin word are called cognates (&lt; cognatus, -a, -um, related), they are related because they both descend from a common PIE word or root, but the English word is derived not from Latin but from another ancient language such as Greek. </t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -3863,7 +3811,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>当英语和拉丁语单词被称为同源词（&lt;cognatus，-a，-um，相关）时，它们是相关的，因为它们都来自一个共同的PIE单词或词根，但英语单词不是来自拉丁语，而是来自另一种古代语言，如希腊语。</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -3884,7 +3832,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>如果一个英语和另一个拉丁语单词源自同一个原始印欧语单词或词根，只是这个英语单词不是直接源自拉丁语，而是另一种古代语言，譬如希腊语，那么我们把这两个单词称为同源词。</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -3905,7 +3853,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Where only the root of an English word is related to the corresponding Latin word, the portion of the English word that descends from that root is boldfaced.2</t>
+          <t>如果一个英语单词与另一个拉丁语单词被称为同源词，那么这也就意味着它们源自同一个原始印欧语单词或词根，只是这个英语单词并非直接源自拉丁语，而是源自另一种古代语言，如古希腊语、古希伯来语等等。</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -3926,7 +3874,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>It is often impossible to tell that a word in Latin and a word in English are cognates because they have undergone radically different changes in pronunciation and spelling as they have developed in their respective language families. For example, the Latin word quinque (five) is cognate with the English word "five," but the words do not appear to be related.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -3947,7 +3895,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">通常不可能说拉丁语中的单词和英语中的单词是同源词，因为它们在各自的语言家族中发展时在发音和拼写方面经历了完全不同的变化。例如，拉丁词quinque（五）与英语单词“five”同源，但这两个词似乎并不相关。  </t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -3968,7 +3916,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>我们一般看不出来哪些单词（从英语和拉丁语中）是同源词，因为它们在各自的语系中发展，发音和拼写上都经历了完全不同的变化。例如，拉丁语单词quique（五）与英语单词five（五）同源，但他们看起来一点也不像</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -3989,7 +3937,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>dominus，domini m</t>
+          <t>（英语与拉丁语的）同源词往往难以辨认，因为其发音和拼写在各自的语系发展中都经历了截然不同的变化。譬如拉丁语单词quinque（五）与英语单词five（五）虽然同源，可看起来却大相径庭。</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -4010,7 +3958,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">In each chapter some English derivatives and cognates of the new Latin vocabulary are listed at the end of the vocabulary notes. These lists are intended in part to help the student remember the meanings of new vocabulary items. </t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -4031,7 +3979,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>在每一章中，词汇注释末尾都列出了一些新拉丁语词汇的英语衍生词和同源词。这些列表部分是为了帮助学生记住新词汇项目的含义。</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -4052,7 +4000,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>为了帮助学生们记住新词汇的含义，我们在每一章词汇注释的末尾都列出了一些新单词与其（在）英语（中的）派生词、同源词。</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -4073,7 +4021,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>各章词汇注释末尾都列有新单词的部分英语派生词与同源词，以便于学生类比记忆。</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -4094,7 +4042,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">They will also help the student expand his or her English vocabulary and stimulate further interest in learning about the relations among words. The cognates are provided to show how the same root or word in PIE has given rise to a wide variety of seemingly unrelated words in English. </t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -4115,7 +4063,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>它们还将帮助学生扩展他或她的英语词汇量，并激发进一步学习单词之间关系的兴趣。提供同源词是为了显示 PIE 中的同一词根或单词如何在英语中产生各种看似无关的单词。</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -4136,7 +4084,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>这也有助于学生拓展英语词汇量，激发他们进一步了解单词间关系的兴趣。而同源词也将展示原始印欧语中同一词根或单词如何产生如此之多看起来无关的英语单词。</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -4157,7 +4105,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>同时这也有助于拓展学生的（英语）词汇量，进而鼓励其探索了解单词彼此之间的关联。另一方面，列出同源词还能向大家展示一个原始印欧语词根或单词如何衍生出大量看似毫不相干的英语单词。</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -4178,7 +4126,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Where only the root of an English word is related to the corresponding Latin word, the portion of the English word that descends from that root is boldfaced.2</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -4199,7 +4147,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> 如果只有英语单词的词根与相应的拉丁词相关，则英语单词中从该词根衍生出来的部分以粗体显示2。</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -4220,7 +4168,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>如果英语单词与相应拉丁语单词间仅有词根相关，我们会用粗体标记出英语单词中由源自该词根的部分</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -4241,7 +4189,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>仅与拉丁语词根相关的英语单词，源自拉丁文词根的部分将以粗体标记。</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -4262,7 +4210,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>dominus，domini m</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -4283,7 +4231,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>ager                                agrarian（农业）            acre（英亩）</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -4304,7 +4252,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>anima                              animate（有活力的 ；使有活力）</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -4325,7 +4273,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">bellum                             bellicose（好战的）  </t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -4346,7 +4294,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>consilium                         counsel（律师；忠告）</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -4367,7 +4315,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">dea, deus                          deity （神）                 July （七月） </t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -4388,7 +4336,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>dominus                           dominate（支配）</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -4409,7 +4357,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">factum                                fact（事实 ）                thesis（论文） </t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -4430,7 +4378,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> fāma                                 famous（著名的）            prophet（先知）; banal（平庸的）</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -4451,7 +4399,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> filia, filius                        affiliate（使隶属）</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -4472,7 +4420,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t xml:space="preserve"> insula                           insulate（使隔绝）; isolate（使孤立）</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -4493,7 +4441,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">S1. The Latin Noun and Its Properties: Gender, Number, Case </t>
+          <t>liber                               library（图书馆）</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -4514,7 +4462,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>nauta                           nautical（航海的）               astronaut（宇航员）; nausea（恶心）</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
@@ -4535,7 +4483,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">pecúnia                       pecuniary（金钱的）                fee（费用） </t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -4556,7 +4504,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A noun is the name of a person, place, or thing.3 Every noun in Latin has three properties: gender, number, and case.</t>
+          <t>periculum                      peril（危险）                   fear（恐惧）; pirate（海盗）</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -4577,7 +4525,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>与</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -4598,7 +4546,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">rēgina                          correct（正确的）,regent（摄政王）                maharajah（土邦主）; right（正确的）; rich（富裕的） </t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -4619,7 +4567,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>verbum                         verb（动词）word（单词）; irony（讽刺）</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -4640,7 +4588,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>GENDER-Latin nouns have the genders masculine or feminine. Nouns that are neither masculine nor feminine are called neuter (&lt; neuter, neutra, neutrum, neither). In the vocabulary entry for each noun, gender is indicated by m., f., or n.</t>
+          <t xml:space="preserve">via                         trivial（琐碎的）, deviate（背离）               way（道路）; weigh（称重） </t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
@@ -4661,7 +4609,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>vir virile,                       virtue（美德）                          werewolf（狼人）; world（世界）</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -4680,11 +4628,7 @@
       <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
@@ -4703,7 +4647,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>拉丁语单词house（domus）</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -4724,7 +4668,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>THIS INFORMATION MUST BE MEMORIZED FOR EACH NOUN.</t>
+          <t>2. 请参阅《美国英语遗产词典》印欧语系词根附录，第 4 版（Houghton-Mifflin，2006 年）来获取这些及其他派生词和同源词的更多信息</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -4745,7 +4689,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>2. 如需获取更多有关上文以及其他派生词与同源词的信息，请参阅 Houghton-Mifflin《美国英语遗产词典（第 4 版）》的印欧语系词根附录。</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -4764,11 +4708,7 @@
       <c r="O207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr"/>
@@ -4787,7 +4727,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>NUMBER-Latin nouns appear in the singular when referring to one and in the plural when referring to more than one.</t>
+          <t>序号47，页数15（拆分：1，Lanx）（机翻：1，Lanx）（人翻：1，Lanx）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -4806,11 +4746,7 @@
       <c r="O209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr"/>
@@ -4829,7 +4765,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">S1. The Latin Noun and Its Properties: Gender, Number, Case </t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -4850,7 +4786,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">S1.拉丁名词及其属性：性别、数字、大小写  </t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -4871,7 +4807,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASE-Latin nouns occur in a variety of different forms in both the singular and the plural. Each different form or case is indicated by a special ending attached to a stem that remains constant. </t>
+          <t>拉丁语名词及其属性：性、数、格</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -4892,7 +4828,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>A noun is the name of a person, place, or thing.3 Every noun in Latin has three properties: gender, number, and case.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -4913,7 +4849,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>domus</t>
+          <t>名词是人、地名或事物的名称.3 拉丁语中的每个名词都有三个属性：性别、数字和大小写</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -4934,7 +4870,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>名词是指人、地区或事物的名称3。拉丁语中，每个名词都有三个属性：性、数、格</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -4955,7 +4891,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>名词即人、地、物或概念的名称. 3. 任何拉丁语名词都拥有三种属性，分别是性、数、格。</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -4976,7 +4912,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>GENDER-Latin nouns have the genders masculine or feminine. Nouns that are neither masculine nor feminine are called neuter (&lt; neuter, neutra, neutrum, neither). In the vocabulary entry for each noun, gender is indicated by m., f., or n.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -4997,7 +4933,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t xml:space="preserve">性别-拉丁名词的性别为男性或女性。既不是男性也不是女性的名词被称为中性（&lt;中性，中性，中性，两者都不是）。在每个名词的词汇条目中，性别用 m.、f 或 n 表示。 </t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -5018,7 +4954,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>同源；也就是说，</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
@@ -5039,7 +4975,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>性属——拉丁语名词区分三种性属：阳性、阴性、中性。【二者皆非（neuter = ne + uter，既不是阳性，也不是阴性），即为中性】</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -5060,7 +4996,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>THIS INFORMATION MUST BE MEMORIZED FOR EACH NOUN.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -5081,7 +5017,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>谨记，必须为每个名词记住此信息</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
@@ -5102,7 +5038,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">The names of the Latin cases and their basic functions are: </t>
+          <t>谨记，必须记住每个名词的性。</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -5123,7 +5059,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>NUMBER-Latin nouns appear in the singular when referring to one and in the plural when referring to more than one.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -5144,7 +5080,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>NUMBER-拉丁名词在指代一个时以单数形式出现，在指代多个时以复数形式出现</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
@@ -5165,7 +5101,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>数——拉丁语名词表示单个数量时使用单数，表示多个数量时使用复数。</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -5186,7 +5122,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>数——拉丁语名词有两种数的变化，即单数与复数。名词在表示单个数量的概念时为单数形式，表示多个数量的概念时为复数形式。</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -5207,7 +5143,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>used for the subiect of a sentence</t>
+          <t xml:space="preserve">CASE-Latin nouns occur in a variety of different forms in both the singular and the plural. Each different form or case is indicated by a special ending attached to a stem that remains constant. </t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
@@ -5228,7 +5164,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>CASE-拉丁名词以单数和复数的多种不同形式出现。每种不同的形式或案例都由一个特殊的结尾表示，该结尾附在保持不变的茎上。</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -5249,7 +5185,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">used for the predicate nominative </t>
+          <t>domus</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -5270,7 +5206,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Each ending indicates the syntax, the grammatical function, that a noun has in a sentence. For example, when a Latin noun serves as the subject of a sentence, it has one case ending, but when it serves as the direct object in a sentence, it has a different case ending.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
@@ -5291,7 +5227,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">The two essential elements of every sentence are the subject and the predicate.The subject is that which is spoken about, and the predicate is all that is said about the subject. For example: </t>
+          <t>每个词尾都表示名词在句子中的语法，语法功能。例如，当一个拉丁名词作为句子的主语时，它有一个大小写结尾，但是当它作为一个句子中的直接宾语时，它有一个不同的大小写结尾</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -5312,7 +5248,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>*并于上句</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -5333,7 +5269,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>John sneezed.</t>
+          <t xml:space="preserve">The parent language of Latin, Indo-European, had eight different cases for nouns, each case with its own grammatical functions. Latin has only six cases, which nevertheless express all the functions of the original eight.4 This is possible because one case in Latin has been made to perform multiple functions. </t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
@@ -5354,7 +5290,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>拉丁语的母语印欧语有八种不同的名词情况，每种情况都有自己的语法功能。拉丁语只有六种情况，但表达了原始八种情况的所有功能.4这是可能的，因为拉丁语中的一个案例已经执行多种功能。</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -5375,7 +5311,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>印欧语作为拉丁语的源语（parent language），它的名词有八个格，每一种都有各自的语法功能。拉丁语虽只有六种，却能表达印欧语八个格的所有语法功能，这是因为拉丁语的格可表达多种语法功能。</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -5396,7 +5332,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>The waiter cleared the dishes from the table.</t>
+          <t>印欧语作为拉丁语的源语（parent language），它的名词有八个格，每一种都有各自的语法功能。拉丁语虽只有六个，但也能表达印欧语八个格的所有语法功能，这是因为拉丁语的每个格都有着多种语法功能。</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
@@ -5417,7 +5353,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>印欧语身为拉丁语的母语，其名词拥有八种格的变化，每一种格都承担着各自的语法功能。相比之下，拉丁语名词只有六种格的变化，即便如此，这六种格也足以承担印欧语那八种格的语法功能。这可能是因为拉丁语的每一种格都承担了丰富多样的语法功能。</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -5438,7 +5374,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t xml:space="preserve">The names of the Latin cases and their basic functions are: </t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -5459,7 +5395,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>拉丁语案例的名称及其基本功能是：</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
@@ -5480,7 +5416,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>拉丁语各格的名称及基本功能有：</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -5501,7 +5437,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3. There are, in fact, several kinds of nouns:</t>
+          <t>Nominative Case</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -5522,7 +5458,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>主格</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
@@ -5543,7 +5479,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>used for the subiect of a sentence</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -5564,7 +5500,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>用作句子主语</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -5585,7 +5521,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>domus</t>
+          <t xml:space="preserve">used for the predicate nominative </t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
@@ -5606,7 +5542,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>用作谓语主格</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -5627,7 +5563,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">The two essential elements of every sentence are the subject and the predicate.The subject is that which is spoken about, and the predicate is all that is said about the subject. For example: </t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -5648,7 +5584,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>句子的两个基本要素是主语和谓语。主语即所叙说的对象，谓语即所叙说的内容。例如：</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -5669,7 +5605,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>John sneezed.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -5690,7 +5626,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>约翰打喷嚏</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -5711,7 +5647,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>张三打了个喷嚏。</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -5732,7 +5668,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>The waiter cleared the dishes from the table.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -5753,7 +5689,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>服务员收拾了桌上的盘子</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -5774,7 +5710,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>In these sentences, "John" and "the waiter" are subjects; "sneezed" and "cleared the dishes from the table" are predicates. Both "John" and "the waiter" would be in the nominative case in Latin, and the syntax of each would be Nominative, Subject.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -5795,7 +5731,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>4. A few Latin nouns have a seventh case, the locative, used to express location in a place</t>
+          <t>在这些句子中，“约翰(John)”和“服务员(The waiter)”是主语;“打喷嚏(sneezed)”和“收拾了桌上的盘子( cleared the dishes from the table.)”是谓词。“约翰”和“服务员”在拉丁语中都是主格，它们的句法都是主语主格（Nominative, Subject.）</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -5816,7 +5752,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>在以上例句中，“张三”和“服务员”是主语;“打了个喷嚏”和“收拾了桌上的盘子”是谓语。以此类推，“张三”和“服务员”在拉丁语中都是主格，其句法为主语主格（Nominative, Subject.）</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -5837,7 +5773,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>3. There are, in fact, several kinds of nouns:</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -5858,7 +5794,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Certain verbs such as "be," "become," and "seem" are called copulative or linking verbs</t>
+          <t>3.名词实际上有以下类别：</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -5879,7 +5815,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>和domus这两个词来自同一个词根。</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -5900,7 +5836,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>普通名词：人、书、城市、饺子（man, book, city, dumpling ）</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
@@ -5921,7 +5857,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A linking verb is never followed by a direct object but rather by an element thatis equivalent to the subject, and the syntax of this element is Predicate Nominative</t>
+          <t>domus</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -5942,7 +5878,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>专有名词：玛丽、意大利、纽约（Mary, Italy, New York ）</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -5963,7 +5899,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>For example: John is a waiter</t>
+          <t>的原意是</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
@@ -5984,7 +5920,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>集体名词：人群、部落、元老院、军队（crowd, tribe, senate, army ）</t>
         </is>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -6005,7 +5941,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>The frog became a prince</t>
+          <t>集体名词/集合名词：人群、部落、参议院、军队（crowd, tribe, senate, army ）</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -6026,7 +5962,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>“家里的主人”</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
@@ -6047,7 +5983,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>In these sentences, "John" and "the frog" are subjects, while "a waiter" and "a prince" are Predicate Nominatives</t>
+          <t>抽象名词：爱、美、奴役、公民身份（love, beauty, slavery, citizenship）</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -6068,7 +6004,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>抽象名词：爱、美、奴隶制、公民身份（love, beauty, slavery, citizenship）</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -6089,7 +6025,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Both the subjects and the Predicate Nominatives would be in the nominative case in Latin</t>
+          <t>&gt;名词dominus, domini (m.)与拉丁语中表示“房屋（house）”的单词domus同源；换言之，dominus与domus均源自同一个词根。dominus本义为“*一家之主”&lt;master of the house&gt;</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -6110,7 +6046,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>动词性名词(verbal nouns)：running(跑)（动名词）、to run(跑)（不定式）</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -6131,7 +6067,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>4. A few Latin nouns have a seventh case, the locative, used to express location in a place</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -6152,7 +6088,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>4.某些拉丁语名词有第七格，即位格，用于表示某地的位置</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -6171,11 +6107,7 @@
       <c r="O274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> -used to qualify or limit another noun in a variety of ways -usually corresponds to a translation using the English preposition "of" In the phrases "the house of friends," "a fear of snakes," and "a jar of pennies," the words "of friends," "of snakes," and "of pennies" qualify or limit in a variety of ways the nouns on which they depend</t>
-        </is>
-      </c>
+      <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr"/>
@@ -6194,7 +6126,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>序号48，页数16（拆分：1，Lanx）（机翻：？，？）（人翻：？，？）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -6213,11 +6145,7 @@
       <c r="O276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>"Of friends," "of snakes," and "of pennies" would be expressed in Latin by "friends," "snakes," and "pennies" in the genitive case with no preposition; that is, the genitive case ending contains the idea of "of" within it</t>
-        </is>
-      </c>
+      <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr"/>
@@ -6236,7 +6164,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Certain verbs such as "be," "become," and "seem" are called copulative or linking verbs</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -6257,7 +6185,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>One idea commonly expressed by the genitive case is that of ownership or possession: "the book of the girl" (= the book belonging to the girl)</t>
+          <t>我们把像"be（是）" "become（变成）" and "seem（看起来）"这样的动词称为系动词</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -6278,7 +6206,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>诸如 “be（是）” “become（变成）” “seem（看起来）”的动词，语法学家称之为系动词（linking verb）</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
@@ -6299,7 +6227,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>The phrase "of the girl" would be expressed in Latin by the word "girl" in the genitive case, and the syntax of that word would be Genitive of Possession</t>
+          <t>A linking verb is never followed by a direct object but rather by an element thatis equivalent to the subject, and the syntax of this element is Predicate Nominative</t>
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -6320,7 +6248,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>系动词后不跟直接宾语，而是需要一个与主语等价的成分，这一成分在句法上称为谓语主格。</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -6341,7 +6269,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>For example: John is a waiter</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
@@ -6362,7 +6290,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>例如，在“John is a waiter（约翰是个服务员）”“The frog became a prince（青蛙变成了王子）”这两句话中，</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -6383,7 +6311,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>-used to express the person or thing interested in or affected by the action of a verb usually corresponds to a translation using the English prepositions "(with reference) to" or "for" In the sentence "</t>
+          <t>The frog became a prince</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -6404,7 +6332,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>*为行文便利，并入上一行</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -6425,7 +6353,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>In these sentences, "John" and "the frog" are subjects, while "a waiter" and "a prince" are Predicate Nominatives</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -6446,7 +6374,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>To the sailor the danger of the sea is real," "to the sailor" expresses the person with reference to whom "the danger of the sea is real</t>
+          <t>“John（约翰）”与“frog（青蛙）”是主语，而“a waiter（服务员）”与“a prince（王子）”是谓语主格（Predicate Nominatives）</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -6467,7 +6395,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Both the subjects and the Predicate Nominatives would be in the nominative case in Latin</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
@@ -6488,7 +6416,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>"The phrase "to the sailor" would be expressed in Latin by the word "sailor" in the dative case with no preposition; that is, the dative case ending contains the notion of "(with reference) to" within it</t>
+          <t>在拉丁语中，它们都用主格</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -6509,7 +6437,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Genitive Case</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -6530,7 +6458,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>The syntax of the word "sailor" in Latin in the dative case would be Dative of Reference</t>
+          <t>属格</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -6551,7 +6479,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> -used to qualify or limit another noun in a variety of ways -usually corresponds to a translation using the English preposition "of" In the phrases "the house of friends," "a fear of snakes," and "a jar of pennies," the words "of friends," "of snakes," and "of pennies" qualify or limit in a variety of ways the nouns on which they depend</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -6572,7 +6500,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>In the sentence "The girl gives a toy to the cat" or "The girl gives the cat a toy," " toy" expresses the direct object of the verb, while "to the cat" or "cat" expresses the indirect object, the person or thing indirectly interested in or affected by the action of the verb</t>
+          <t>{*尝试让译文更符合汉语风格}</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -6593,7 +6521,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>"Of friends," "of snakes," and "of pennies" would be expressed in Latin by "friends," "snakes," and "pennies" in the genitive case with no preposition; that is, the genitive case ending contains the idea of "of" within it</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -6614,7 +6542,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Again, "to the cat" or "cat" would be expressed in Latin in the dative case with no preposition, and the syntax of that word would be Dative of Indirect Object</t>
+          <t>在拉丁语中，这些词采用属格且无需介词，属格的词尾包含了介词“of”这一含义</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -6635,7 +6563,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>One idea commonly expressed by the genitive case is that of ownership or possession: "the book of the girl" (= the book belonging to the girl)</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -6656,7 +6584,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>This use of the dative case appears most often with verbs of giving, showing, and telling</t>
+          <t>属格常用于表达“拥有”这一概念："the book of the girl"（女孩的书，即这本书属于这个女孩）</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -6677,7 +6605,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>The phrase "of the girl" would be expressed in Latin by the word "girl" in the genitive case, and the syntax of that word would be Genitive of Possession</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -6698,7 +6626,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>在拉丁语中，我们会用“girl（女孩）”的属格来表达“of the girl（女孩的）”这一短语，而这一成分在句法上称为物主属格（Genitive of Possession）。</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -6719,7 +6647,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t xml:space="preserve">Dative Case </t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
@@ -6740,7 +6668,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>与格</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -6761,7 +6689,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t xml:space="preserve"> -used for the direct object of a verb  </t>
+          <t>-used to express the person or thing interested in or affected by the action of a verb usually corresponds to a translation using the English prepositions "(with reference) to" or "for" In the sentence "</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -6782,7 +6710,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>若一个介词的后置单词为宾格，那么我们说这个介词</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -6803,7 +6731,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>used following certain prepositions</t>
+          <t>用于表达间接受到关注的对象或受动作影响的人或物，在英语中常以介词“(with reference) to”“for”翻译。</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -6824,7 +6752,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>To the sailor the danger of the sea is real," "to the sailor" expresses the person with reference to whom "the danger of the sea is real</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -6845,7 +6773,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>In the sentence "The poet writes poems," "poems" is the direct object of the verb "writes" because the action of the verb "writes" is directly exerted on the object "poems</t>
+          <t>在“To the sailor the danger of the sea is real（对水手来说，海洋的确是危险的）”中，“to the sailor（对水手来说）”明确了对“谁”来说“the danger of the sea is real（海洋是危险的）”。</t>
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
@@ -6866,7 +6794,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>"The phrase "to the sailor" would be expressed in Latin by the word "sailor" in the dative case with no preposition; that is, the dative case ending contains the notion of "(with reference) to" within it</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -6887,7 +6815,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>" The word "poems" would be expressed in Latin in the accusative case, and the syntax of that word would be Accusative, Direct Object</t>
+          <t>“取宾格”</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -6908,7 +6836,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>The syntax of the word "sailor" in Latin in the dative case would be Dative of Reference</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
@@ -6929,7 +6857,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>In addition to being used to express the direct object of a verb, the accusative case follows prepositions that express motion toward, into, around, and through</t>
+          <t>这一成分在句法上称为关系与格（Dative of Reference）</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -6950,7 +6878,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>In the sentence "The girl gives a toy to the cat" or "The girl gives the cat a toy," " toy" expresses the direct object of the verb, while "to the cat" or "cat" expresses the indirect object, the person or thing indirectly interested in or affected by the action of the verb</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -6971,7 +6899,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>For example, to express the phrase "toward the field" in Latin, the preposition ad (toward) is followed by the word "field" in Latin in the accusative case</t>
+          <t>在“The girl gives a toy to the cat（女孩把玩具给了猫）”或“The girl gives the cat a toy(女孩给了猫玩具)”中，“toy（玩具）”是动词的直接宾语，而“to the cat（猫）”“cat（猫）”是间接宾语，即间接受关注的对象或间接受动词影响的一方。</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
@@ -6992,7 +6920,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Again, "to the cat" or "cat" would be expressed in Latin in the dative case with no preposition, and the syntax of that word would be Dative of Indirect Object</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -7013,7 +6941,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>我们同样用与格来表达“to the cat（猫）”或“cat（猫）”这一短语，而这一成分在句法上称为间接宾语与格（Dative of Indirect Object），常搭配有“给予”“展示”“诉说”这类含义的动词使用。</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -7034,7 +6962,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>This use of the dative case appears most often with verbs of giving, showing, and telling</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
@@ -7055,7 +6983,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t xml:space="preserve"> used to express separation (original function of the ablative case); in this usage, corresponds to a translation using the English preposition "from" </t>
+          <t>*为行文便利，并入上一行</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -7076,7 +7004,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>序号49，页数17（拆分：1，Lanx）（机翻：？，？）（人翻：？，？）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -7095,11 +7023,7 @@
       <c r="O318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-also expresses association or instrument; in this usage, corresponds to a translation using the English prepositions "with" or "by" </t>
-        </is>
-      </c>
+      <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr"/>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr"/>
@@ -7118,7 +7042,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> Accusative Case</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -7139,7 +7063,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t xml:space="preserve"> -also expresses location (in space or time);in this usage, corresponds to a translation using the English prepositions "in," "on," or "at" </t>
+          <t>宾格</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -7160,7 +7084,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> -used for the direct object of a verb  </t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -7181,7 +7105,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Separation</t>
+          <t>用于动词的直接宾语，常置于某些介词后</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -7202,7 +7126,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>used following certain prepositions</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -7223,7 +7147,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>In the sentence "He came from Italy," the phrase "from Italy" expresses motion from a place: "he" is separated from "Italy</t>
+          <t>*为行文便利，并入上一行</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
@@ -7244,7 +7168,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>In the sentence "The poet writes poems," "poems" is the direct object of the verb "writes" because the action of the verb "writes" is directly exerted on the object "poems</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -7265,7 +7189,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>In the sentence "The king freed the people from slavery," "the people" are separated from "slavery</t>
+          <t>在“"The poet writes poems（诗人写诗）”中，因为“write（写）这一动作直接施事于“poem（诗）”，所以后者是前者直接宾语</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -7286,7 +7210,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>" The word "poems" would be expressed in Latin in the accusative case, and the syntax of that word would be Accusative, Direct Object</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
@@ -7307,7 +7231,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>These two examples suggest the range of meaning expressed by the ablative's separative function</t>
+          <t>在拉丁语中，我们会用“poem（诗）”的宾格来表达上述内涵，而这一成分在句法上称为直接宾语（Accusative, Direct Object）</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -7328,7 +7252,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>In addition to being used to express the direct object of a verb, the accusative case follows prepositions that express motion toward, into, around, and through</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -7349,7 +7273,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>The idea of going from a place (out from/away from/down from) usually requires a preposition and a noun in the ablative case</t>
+          <t xml:space="preserve">，在单词表中标记为   </t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
@@ -7370,7 +7294,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>For example, to express the phrase "toward the field" in Latin, the preposition ad (toward) is followed by the word "field" in Latin in the accusative case</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -7391,7 +7315,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Thus, in the example above, "from Italy" would be expressed in Latin by the preposition ab ((away] from) and "Italy" in the ablative case</t>
+          <t>例如，在拉丁语中，我们会把“field（田）”的宾格写在ad（toward，向）之后，以此表达“toward the field（向田里）”这一短语。</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -7412,7 +7336,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Ablative Case</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -7433,7 +7357,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>The idea of "from slavery" in the second example would be expressed by the word "slavery" in the ablative case and might be accompanied by a preposition</t>
+          <t>离格</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -7454,7 +7378,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> used to express separation (original function of the ablative case); in this usage, corresponds to a translation using the English preposition "from" </t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -7475,7 +7399,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Association/Instrument </t>
+          <t>表分离（离格最初的功能）；在翻译这种离格时，常用英语中的介词“from”</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
@@ -7496,7 +7420,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">-also expresses association or instrument; in this usage, corresponds to a translation using the English prepositions "with" or "by" </t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -7517,7 +7441,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>In the sentence "The woman came to the party with a poet," the phrase "with a poet" indicates that the woman was accompanied by a poet</t>
+          <t xml:space="preserve"> ？（介+宾）</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -7538,7 +7462,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> -also expresses location (in space or time);in this usage, corresponds to a translation using the English prepositions "in," "on," or "at" </t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
@@ -7559,7 +7483,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>The phrase "with a poet”would be expressed in Latin by the preposition cum (with) and "poet" in the ablative case; the syntax of that word would be Ablative of Accompaniment</t>
+          <t>表位置；在翻译这种离格时，常用英语中的介词“in”“on”或“at”</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -7580,7 +7504,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Separation</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -7601,7 +7525,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>NOTE THAT THE ABLATIVE OF ACCOMPANIMENT REQUIRES THE PREPOSITION CUM</t>
+          <t>分离</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -7622,7 +7546,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>In the sentence "He came from Italy," the phrase "from Italy" expresses motion from a place: "he" is separated from "Italy</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -7643,7 +7567,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>In the sentence "The farmer is fighting with a sword," the phrase "with a sword" indicates what the farmer uses to fight, or the instrument by means of which he is fighting</t>
+          <t>取宾格的介词用于强调</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -7664,7 +7588,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>In the sentence "The king freed the people from slavery," "the people" are separated from "slavery</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -7685,7 +7609,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>The phrase "with a sword" would be expressed in Latin by the word "sword" in the ablative case with no preposition; the syntax of that word would be Ablative of Means (or Ablative of Instrument)</t>
+          <t>在“The king freed the people from slavery,（国王将人们从奴役中解放）”中，“people（人们）”从“slavery（奴役中）”分离</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -7706,7 +7630,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>These two examples suggest the range of meaning expressed by the ablative's separative function</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -7727,7 +7651,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>NOTE THAT NO PREPOSITION IS USED WITH THE ABLATIVE OF MEANS</t>
+          <t>这个两个例子表明了离格表分离这一功能的适用范围。</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -7748,7 +7672,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>The idea of going from a place (out from/away from/down from) usually requires a preposition and a noun in the ablative case</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -7769,7 +7693,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>我们通常用介词与名词的离格来表达从某地离开这一概念。</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -7790,7 +7714,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Location </t>
+          <t>Thus, in the example above, "from Italy" would be expressed in Latin by the preposition ab ((away] from) and "Italy" in the ablative case</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -7811,7 +7735,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>因此，在拉丁语中，我们会用介词ab（远离）与“Italy（意大利）”的离格来表达短语“from Italy（自意大利）”。</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -7832,7 +7756,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>In the sentences "Farmers work in fields" and "The queen lives on an island," the phrases "in fields" and "on an island" express ideas of location or place where</t>
+          <t>The idea of "from slavery" in the second example would be expressed by the word "slavery" in the ablative case and might be accompanied by a preposition</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -7853,7 +7777,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>而我们在表达短语“from slavery（从奴役中）”时，有可能不加介词，仅使用“slavery（奴役中）”的离格</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -7874,7 +7798,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>The phrases "in fields" and "on an island" would be expressed in Latin by the preposition in (in, on) and the words "fields" and "island" in the ablative case</t>
+          <t xml:space="preserve">Association/Instrument </t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -7895,7 +7819,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>表连携或表手段</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -7916,7 +7840,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>NOTE THAT SUCH AN ABLATIVE REQUIRES THE PREPOSITION IN</t>
+          <t>In the sentence "The woman came to the party with a poet," the phrase "with a poet" indicates that the woman was accompanied by a poet</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -7937,7 +7861,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>在“The woman came to the party with a poet（女人与诗人参加了派对）”中，短语“with a poet（与诗人）”表明这个女人由诗人陪同。</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -7958,7 +7882,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>The phrase "with a poet”would be expressed in Latin by the preposition cum (with) and "poet" in the ablative case; the syntax of that word would be Ablative of Accompaniment</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -7979,7 +7903,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>在拉丁语中，我们会用介词cum（与）和“poet（诗人）”的离格来表达上述短语，而这一成分在句法上称为伴随离格（Ablative of Accompaniment）</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
@@ -8000,7 +7924,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t xml:space="preserve">--used for addressing someone directly </t>
+          <t>NOTE THAT THE ABLATIVE OF ACCOMPANIMENT REQUIRES THE PREPOSITION CUM</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -8021,7 +7945,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>谨记，伴随离格须搭配介词cum使用。</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -8042,7 +7966,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>In the sentence "Tell me, father, why you have come," the word "father" expresses the person being directly addressed by the speaker of the sentence</t>
+          <t>In the sentence "The farmer is fighting with a sword," the phrase "with a sword" indicates what the farmer uses to fight, or the instrument by means of which he is fighting</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -8063,7 +7987,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>在“The farmer is fighting with a sword（农民正在用剑战斗）”中，短语“with a sword（用剑）”表明了农民战斗所用的工具，或者说，他战斗所用的手段。</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -8084,7 +8008,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>The word "father" would be expressed in Latin in the vocative case</t>
+          <t>The phrase "with a sword" would be expressed in Latin by the word "sword" in the ablative case with no preposition; the syntax of that word would be Ablative of Means (or Ablative of Instrument)</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -8105,7 +8029,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>在拉丁语中，我们无需介词，仅用“sword（剑）”的离格便能表达短语“with a sword（用剑）”，而这一成分在句法上称为手段离格（Ablative of Means，或工具离格， Ablative of Instrument）</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
@@ -8126,7 +8050,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>In Latin, a word in the vocative case is sometimes preceded by the interjection o (O)</t>
+          <t>NOTE THAT NO PREPOSITION IS USED WITH THE ABLATIVE OF MEANS</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -8147,7 +8071,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>谨记，手段离格无须搭配介词使用。</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -8166,11 +8090,7 @@
       <c r="O369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Summary of Cases and Their Basic Functions</t>
-        </is>
-      </c>
+      <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr"/>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr"/>
@@ -8187,11 +8107,7 @@
       <c r="O370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr"/>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr"/>
@@ -8210,7 +8126,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Case Name   Used to Express </t>
+          <t>序号50，页数18（拆分：1，Lanx）（机翻：？，？）（人翻：？，？）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -8229,11 +8145,7 @@
       <c r="O372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr"/>
@@ -8252,7 +8164,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">Location </t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -8273,7 +8185,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nominative   1. subject </t>
+          <t>表位置</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -8294,7 +8206,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>In the sentences "Farmers work in fields" and "The queen lives on an island," the phrases "in fields" and "on an island" express ideas of location or place where</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -8315,7 +8227,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t xml:space="preserve">                     2. predicate nominative</t>
+          <t>在“Farmers work in fields（农民在田里劳作）”与“The queen lives on an island（女王住在岛上）”，短语“in fields（在田里）”和“on an island（在岛上）”表达着位置这一概念</t>
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -8336,7 +8248,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>The phrases "in fields" and "on an island" would be expressed in Latin by the preposition in (in, on) and the words "fields" and "island" in the ablative case</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -8357,7 +8269,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genitive       "of" </t>
+          <t>在拉丁语中，我们会用介词in（于其中或于其上）与“fields（田）”和“island（岛）”的离格来表达短语“in fields（在田里）”和“on an island（在岛上）”，</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -8378,7 +8290,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>NOTE THAT SUCH AN ABLATIVE REQUIRES THE PREPOSITION IN</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -8399,7 +8311,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Dative         "to," "for"</t>
+          <t>谨记，这类离格须搭配介词使用。</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -8420,7 +8332,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">Vocative Case </t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -8441,7 +8353,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Accusative   1. direct object</t>
+          <t>呼格</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -8462,7 +8374,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">--used for addressing someone directly </t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -8483,7 +8395,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    2. with certain prepositions </t>
+          <t>用于直接称呼某人</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -8504,7 +8416,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>In the sentence "Tell me, father, why you have come," the word "father" expresses the person being directly addressed by the speaker of the sentence</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -8525,7 +8437,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Ablative       1. "from"</t>
+          <t>在“Tell me, father, why you have come（告诉我，父亲，你为什么过来了）”中，“father（父亲）”一词表明了发话者直接称呼的对象</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -8546,7 +8458,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>The word "father" would be expressed in Latin in the vocative case</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
@@ -8567,7 +8479,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    2. "with,"  "by (means of"</t>
+          <t>在拉丁语中，该词采用呼格。</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -8588,7 +8500,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>In Latin, a word in the vocative case is sometimes preceded by the interjection o (O)</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -8609,7 +8521,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    3. "in" "on"</t>
+          <t>采用呼格的词前可能会有叹词o</t>
         </is>
       </c>
       <c r="B391" t="inlineStr"/>
@@ -8630,7 +8542,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Summary of Cases and Their Basic Functions</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -8651,7 +8563,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>格与其基本功能的总结</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -8672,7 +8584,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t xml:space="preserve">Case Name   Used to Express </t>
         </is>
       </c>
       <c r="B394" t="inlineStr"/>
@@ -8693,7 +8605,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DRILL 1, PAGE 7, MAY NOW BE DONE</t>
+          <t>名称                 用于</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -8714,7 +8626,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>名称                 用途</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -8735,7 +8647,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t xml:space="preserve">§2 The Five Declensions </t>
+          <t xml:space="preserve">Nominative   1. subject </t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
@@ -8756,7 +8668,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>主格              1.主语</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -8777,7 +8689,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">                     2. predicate nominative</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -8798,7 +8710,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Latin nouns are grouped in five different families called declensions</t>
+          <t xml:space="preserve">                     2.谓语主格</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
@@ -8819,7 +8731,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">Genitive       "of" </t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -8840,7 +8752,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Each noun belongs to one declension only, and each declension has its own distinctive set of case endings</t>
+          <t>属格             代替英语中的介词“of”</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -8861,7 +8773,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Dative         "to," "for"</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
@@ -8882,7 +8794,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>The five groups of nouns are most reliably distinguished and identified by the genitive singular ending of each declension:</t>
+          <t>与格            代替英语中的介词“to”“for”</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -8903,7 +8815,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Accusative   1. direct object</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -8924,7 +8836,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>宾格             1.直接宾语</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
@@ -8945,7 +8857,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t xml:space="preserve">                    2. with certain prepositions </t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -8966,7 +8878,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t xml:space="preserve">1st declension   -ae </t>
+          <t xml:space="preserve">                    2.搭配特定介词</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -8987,7 +8899,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>Ablative       1. "from"</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
@@ -9008,7 +8920,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2nd declension  -ī</t>
+          <t>离格             1.代替英语中的介词“from”</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -9029,7 +8941,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">                    2. "with,"  "by (means of"</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -9050,7 +8962,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>3rd declension   -is</t>
+          <t xml:space="preserve">                    2.代替英语中的介词“with”“by（手段）”</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
@@ -9071,7 +8983,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">                    3. "in" "on"</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -9092,7 +9004,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>4th declension   -ūs</t>
+          <t xml:space="preserve">                    3.代替英语中的介词“in”“on”</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -9113,7 +9025,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> Vocative     direct address</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
@@ -9134,7 +9046,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>5th declension   -eī/-ēī</t>
+          <t>呼格             直接称呼</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -9155,7 +9067,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> DRILL 1, PAGE 7, MAY NOW BE DONE</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -9176,7 +9088,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>略</t>
         </is>
       </c>
       <c r="B418" t="inlineStr"/>
@@ -9197,7 +9109,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t xml:space="preserve">§2 The Five Declensions </t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -9218,7 +9130,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t xml:space="preserve">A full vocabulary entry for a Latin noun contains, in the following order, the nominative singular, the genitive singular, a notation of gender, and the English meaning(s). For example: </t>
+          <t>§2 五大变格</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -9239,7 +9151,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>§2 五大变格法</t>
         </is>
       </c>
       <c r="B421" t="inlineStr"/>
@@ -9260,7 +9172,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>Latin nouns are grouped in five different families called declensions</t>
         </is>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -9281,7 +9193,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>servus, servī m. slave</t>
+          <t>拉丁语名词分为五类，称为五大变格</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -9297,16 +9209,12 @@
       <c r="L423" t="inlineStr"/>
       <c r="M423" t="inlineStr"/>
       <c r="N423" t="inlineStr"/>
-      <c r="O423" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
+      <c r="O423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>Each noun belongs to one declension only, and each declension has its own distinctive set of case endings</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
@@ -9327,7 +9235,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t xml:space="preserve">perīculum, perīculī n;  danger </t>
+          <t>每个名词都属于且仅属于一种变格，而每一类变格都有一套不同的格尾（格的词尾，简称格尾，下同）</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -9348,7 +9256,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>OBSERVATIONS</t>
+          <t>The five groups of nouns are most reliably distinguished and identified by the genitive singular ending of each declension:</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -9369,7 +9277,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>大多数情况下，这五类名词可通过每一变格的属格单数词尾区分</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
@@ -9390,7 +9298,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t xml:space="preserve">                           Genitive Singular Ending</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -9411,7 +9319,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>属格单数词尾</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -9432,7 +9340,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t xml:space="preserve">1st declension   -ae </t>
         </is>
       </c>
       <c r="B430" t="inlineStr"/>
@@ -9453,7 +9361,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>第一变格 -ae</t>
         </is>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -9474,7 +9382,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Even though the endings of their nominative singular forms differ, the endings of the genitive singular forms do not</t>
+          <t>2nd declension  -ī</t>
         </is>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -9495,7 +9403,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>第二变格 -ī</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
@@ -9516,7 +9424,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Finding the Stem</t>
+          <t>3rd declension   -is</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -9537,7 +9445,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>第三变格 -is</t>
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -9558,7 +9466,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The genitive singular is given in the vocabulary for purposes of identifying the declension to which each noun belongs, but the genitive singular is also the form from which a stem is derived for use in making all other forms of the noun</t>
+          <t>4th declension   -ūs</t>
         </is>
       </c>
       <c r="B436" t="inlineStr"/>
@@ -9579,7 +9487,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>第四变格 -ūs</t>
         </is>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -9600,7 +9508,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>To find the stem of any noun, remove the ending from the genitive singular (the second element given in the vocabulary). What remains is the stem</t>
+          <t>5th declension   -eī/-ēī</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -9621,7 +9529,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>第五变格 -eī/-ēī</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
@@ -9640,11 +9548,7 @@
       <c r="O439" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A440" t="inlineStr"/>
       <c r="B440" t="inlineStr"/>
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr"/>
@@ -9663,7 +9567,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>快拆分~~</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -9684,7 +9588,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>liber, libr/ī m. book            stem = libr-</t>
+          <t>序号51，页数19（拆分：？，？）（机翻：？，？）（人翻：？，？）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
@@ -9703,11 +9607,7 @@
       <c r="O442" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>servus, serv/ī m. slave     stem = serv-</t>
-        </is>
-      </c>
+      <c r="A443" t="inlineStr"/>
       <c r="B443" t="inlineStr"/>
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr"/>
@@ -9726,7 +9626,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t xml:space="preserve">A full vocabulary entry for a Latin noun contains, in the following order, the nominative singular, the genitive singular, a notation of gender, and the English meaning(s). For example: </t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -9747,7 +9647,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>All the forms of a noun are created by taking the stem of that noun and adding the case endings that belong to its particular declension</t>
+          <t>完整的拉丁语名词词条，按下列顺序，包含着主格单数，属格单数，性，与意义</t>
         </is>
       </c>
       <c r="B445" t="inlineStr"/>
@@ -9768,7 +9668,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">puella, puellae f. girl </t>
         </is>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -9789,7 +9689,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>When one generates a complete set of forms for a noun in Latin, one is said to decline the noun, and the resulting set of forms is called a declension of the noun</t>
+          <t>servus, servī m. slave</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -9805,12 +9705,16 @@
       <c r="L447" t="inlineStr"/>
       <c r="M447" t="inlineStr"/>
       <c r="N447" t="inlineStr"/>
-      <c r="O447" t="inlineStr"/>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> vir, virī m. man; husband </t>
         </is>
       </c>
       <c r="B448" t="inlineStr"/>
@@ -9831,7 +9735,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>§3  Noun Morphology: First Declension</t>
+          <t xml:space="preserve">perīculum, perīculī n;  danger </t>
         </is>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -9850,11 +9754,7 @@
       <c r="O449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A450" t="inlineStr"/>
       <c r="B450" t="inlineStr"/>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr"/>
@@ -9873,7 +9773,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Gender Note: Most nouns of the first declension are feminine, some are masculine. There are no neuter first-declension nouns</t>
+          <t>OBSERVATIONS</t>
         </is>
       </c>
       <c r="B451" t="inlineStr"/>
@@ -9894,7 +9794,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>注意</t>
         </is>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -9915,7 +9815,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Case Endings of the First Declension</t>
+          <t>1. The -ae ending on the genitive singular of puella indicates that this noun belongs to the first declension</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -9936,7 +9836,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>1.puella的属格单数词尾-ae表明这一名词属于第一变格</t>
         </is>
       </c>
       <c r="B454" t="inlineStr"/>
@@ -9957,7 +9857,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>2.The -i endings on the genitive singular forms of servus, vir, and periculum indicate that these nouns all belong to the second declension</t>
         </is>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -9978,7 +9878,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>2.servus，vir，periculum的属格单数词尾-i表明这些名词均属于第二变格</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -9999,7 +9899,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Nominative/Vocative  -a            -ae</t>
+          <t xml:space="preserve"> Even though the endings of their nominative singular forms differ, the endings of the genitive singular forms do not</t>
         </is>
       </c>
       <c r="B457" t="inlineStr"/>
@@ -10020,7 +9920,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Genitive                    -ae           -ārum</t>
+          <t>虽然它们的主格单数词尾不同，但是它们的属格单数词尾一致</t>
         </is>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -10041,7 +9941,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dative                       -ae           -īs</t>
+          <t>Finding the Stem</t>
         </is>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -10062,7 +9962,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Accusative                 -am         -ās</t>
+          <t>找出词干</t>
         </is>
       </c>
       <c r="B460" t="inlineStr"/>
@@ -10083,7 +9983,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Ablative                      -ā            -īs</t>
+          <t xml:space="preserve"> The genitive singular is given in the vocabulary for purposes of identifying the declension to which each noun belongs, but the genitive singular is also the form from which a stem is derived for use in making all other forms of the noun</t>
         </is>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -10104,7 +10004,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 5.There are thus two meanings for the word "declension": 1. the name for each of the five families of nouns (first declension, second declension, etc); </t>
+          <t>出于辨认名词变格的目的，单词表中每个名词词条包含着属格单数，而我们也借助名词的这一形式来找出词干用以构词</t>
         </is>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -10125,7 +10025,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>To find the stem of any noun, remove the ending from the genitive singular (the second element given in the vocabulary). What remains is the stem</t>
         </is>
       </c>
       <c r="B463" t="inlineStr"/>
@@ -10146,7 +10046,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>1. the name for each of the five families of nouns (first declension, second declension, etc);</t>
+          <t>对于任意一个名词，将其属格单数词尾除去后余下的部分便是词干。</t>
         </is>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -10167,7 +10067,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>“前往”“进入”“环绕”“通过”</t>
         </is>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -10188,7 +10088,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2. a complete set of forms for an individual noun.</t>
+          <t>puella, puell/ae f. girl        stem = puell-</t>
         </is>
       </c>
       <c r="B466" t="inlineStr"/>
@@ -10209,7 +10109,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>liber, libr/ī m. book            stem = libr-</t>
         </is>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -10230,7 +10130,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>servus, serv/ī m. slave     stem = serv-</t>
         </is>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -10251,7 +10151,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>MEMORIZE THESE ENDINGS THOROUGHIY, PROCEEDING FIRST DOWN THE SINGULAR COLUMN AND THEN DOWN THE PIURAL COIUMN. BE PREPARED TO RECITE THE ENDINGS QUICKIY.</t>
+          <t>vir, vir/ī m. man; husband steam = vir-</t>
         </is>
       </c>
       <c r="B469" t="inlineStr"/>
@@ -10270,11 +10170,7 @@
       <c r="O469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr"/>
       <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr"/>
@@ -10293,7 +10189,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t xml:space="preserve">To decline a noun of the first declension, add these endings to the stem.  For example: </t>
+          <t>All the forms of a noun are created by taking the stem of that noun and adding the case endings that belong to its particular declension</t>
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -10314,7 +10210,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>我们可通过在名词词干上添加对应变格格尾这一方式来构建名词的所有形式</t>
         </is>
       </c>
       <c r="B472" t="inlineStr"/>
@@ -10335,7 +10231,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>When one generates a complete set of forms for a noun in Latin, one is said to decline the noun, and the resulting set of forms is called a declension of the noun</t>
         </is>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -10356,7 +10252,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t xml:space="preserve"> stem = puell-</t>
+          <t>列出一个名词成套的形式这一行为称为对名词进行变格，所列之物称为这一名词的变格</t>
         </is>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -10377,7 +10273,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                   Singular</t>
+          <t>§3  Noun Morphology: First Declension</t>
         </is>
       </c>
       <c r="B475" t="inlineStr"/>
@@ -10398,7 +10294,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>§3  名词词法：第一变格</t>
         </is>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -10419,7 +10315,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Gender Note: Most nouns of the first declension are feminine, some are masculine. There are no neuter first-declension nouns</t>
         </is>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -10440,7 +10336,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>关于性：绝大多数的第一变格名词都是阴性，其余为阳性。没有中性第一变格名词</t>
         </is>
       </c>
       <c r="B478" t="inlineStr"/>
@@ -10461,7 +10357,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Case Endings of the First Declension</t>
         </is>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -10482,7 +10378,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>第一变格格尾</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -10503,7 +10399,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t xml:space="preserve">                                Singular  Plural</t>
         </is>
       </c>
       <c r="B481" t="inlineStr"/>
@@ -10524,7 +10420,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>单数 复数</t>
         </is>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -10545,7 +10441,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>Nominative/Vocative  -a            -ae</t>
         </is>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -10566,7 +10462,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>Genitive                    -ae           -ārum</t>
         </is>
       </c>
       <c r="B484" t="inlineStr"/>
@@ -10587,7 +10483,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t xml:space="preserve"> Dative                       -ae           -īs</t>
         </is>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -10608,7 +10504,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                   Plural</t>
+          <t>Accusative                 -am         -ās</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -10629,7 +10525,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nom. /Voc.   puellae                 the girls (subj. or pred. nom.)girls (d.a.)</t>
+          <t>Ablative                      -ā            -īs</t>
         </is>
       </c>
       <c r="B487" t="inlineStr"/>
@@ -10648,11 +10544,7 @@
       <c r="O487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A488" t="inlineStr"/>
       <c r="B488" t="inlineStr"/>
       <c r="C488" t="inlineStr"/>
       <c r="D488" t="inlineStr"/>
@@ -10671,7 +10563,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t xml:space="preserve"> 5.There are thus two meanings for the word "declension": 1. the name for each of the five families of nouns (first declension, second declension, etc); </t>
         </is>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -10692,7 +10584,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>5.因而变格一词有着两个含义：</t>
         </is>
       </c>
       <c r="B490" t="inlineStr"/>
@@ -10713,7 +10605,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>1. the name for each of the five families of nouns (first declension, second declension, etc);</t>
         </is>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -10734,7 +10626,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t xml:space="preserve">A few prepositions can take either case,and </t>
+          <t>1.指五大变格中的一类</t>
         </is>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -10755,7 +10647,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>2. a complete set of forms for an individual noun.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr"/>
@@ -10776,7 +10668,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>their meanings differ according to which case they take.</t>
+          <t>2.一个名词成套的形式</t>
         </is>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -10795,11 +10687,7 @@
       <c r="O494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>【表格】</t>
-        </is>
-      </c>
+      <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr"/>
       <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr"/>
@@ -10818,7 +10706,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt;ad takes the accusative and expresses motion to or toward a </t>
+          <t>序号52，页数20（拆分：？，？）（机翻：？，？）（人翻：？，？）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
         </is>
       </c>
       <c r="B496" t="inlineStr"/>
@@ -10837,11 +10725,7 @@
       <c r="O496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OBSERVATIONS </t>
-        </is>
-      </c>
+      <c r="A497" t="inlineStr"/>
       <c r="B497" t="inlineStr"/>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
@@ -10860,7 +10744,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>MEMORIZE THESE ENDINGS THOROUGHIY, PROCEEDING FIRST DOWN THE SINGULAR COLUMN AND THEN DOWN THE PIURAL COIUMN. BE PREPARED TO RECITE THE ENDINGS QUICKIY.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -10881,7 +10765,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.The abbreviations for the case names used in the model declension above are standard and appear frequently in this book, as do the abbreviations subj.(subject), pred.nom.(predicate nominative), d. a.(direct address), and d. o.(direct object). </t>
+          <t>谨记，牢记这些词尾，按列先后记住单数与复数。要能够快速复述它们。</t>
         </is>
       </c>
       <c r="B499" t="inlineStr"/>
@@ -10902,7 +10786,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">To decline a noun of the first declension, add these endings to the stem.  For example: </t>
         </is>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -10923,7 +10807,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2.In the first declension, as in most other declensions, the nominative and vocative endings in both singular and plural are identical and are therefore listed together. </t>
+          <t>通过在词干上添加下列词尾来对第一变格名词进行变格。例如：</t>
         </is>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -10944,7 +10828,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>这些概念</t>
         </is>
       </c>
       <c r="B502" t="inlineStr"/>
@@ -10965,7 +10849,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> stem = puell-</t>
         </is>
       </c>
       <c r="B503" t="inlineStr"/>
@@ -10986,7 +10870,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.Certain endings of the first declension are used to mark more than one case: -ae = genitive singular, dative singular, and nominative/vocative plural; -is = dative plural and ablative plural. </t>
+          <t xml:space="preserve">                                                   Singular</t>
         </is>
       </c>
       <c r="B504" t="inlineStr"/>
@@ -11007,7 +10891,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">Nom. /Voc.    puella                    the girl (subject or predicate nominative) girl (direct address) </t>
         </is>
       </c>
       <c r="B505" t="inlineStr"/>
@@ -11028,7 +10912,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALWAYS CONSIDER ALL POSSIBILITIES WHEN IDENTIFYING THE FORM OF A NOUN. </t>
+          <t>主/呼             puella                    女孩（主语或谓语主格）/女孩（直接称呼）</t>
         </is>
       </c>
       <c r="B506" t="inlineStr"/>
@@ -11049,7 +10933,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">Gen.             puellae                 of the girl </t>
         </is>
       </c>
       <c r="B507" t="inlineStr"/>
@@ -11070,7 +10954,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context usually makes clear which form occurs in a particular sentence. </t>
+          <t>：例如，vir feminaque（丈夫</t>
         </is>
       </c>
       <c r="B508" t="inlineStr"/>
@@ -11091,7 +10975,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Dat.                puellae                to the girl/for the girl</t>
         </is>
       </c>
       <c r="B509" t="inlineStr"/>
@@ -11112,7 +10996,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 4. Two first-declension words in the vocabulary of this chapter, dea, deae f. , "goddess," and filia, filiae f. , "daughter," occasionally have irregular dative and ablative plural forms: deabus and filiabus, but these forms do not appear in this textbook. </t>
+          <t>“取离格”</t>
         </is>
       </c>
       <c r="B510" t="inlineStr"/>
@@ -11133,7 +11017,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Acc.               puellam                the girl (direct object)</t>
         </is>
       </c>
       <c r="B511" t="inlineStr"/>
@@ -11154,7 +11038,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 5.The Latin language has no definite article (the) and no indefinite article (a, an).  English definite or indefinite articles mav be freely added in translations of Latin nouns as context demands. </t>
+          <t>宾                 puellam                女孩（直接宾语）</t>
         </is>
       </c>
       <c r="B512" t="inlineStr"/>
@@ -11175,7 +11059,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>place. Compare</t>
+          <t xml:space="preserve">Abl.               puella                     from the girl; by/with the girl; in the girl </t>
         </is>
       </c>
       <c r="B513" t="inlineStr"/>
@@ -11196,7 +11080,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>，标记为</t>
         </is>
       </c>
       <c r="B514" t="inlineStr"/>
@@ -11217,7 +11101,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t xml:space="preserve">                                                   Plural</t>
         </is>
       </c>
       <c r="B515" t="inlineStr"/>
@@ -11238,7 +11122,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t xml:space="preserve"> Nom. /Voc.   puellae                 the girls (subj. or pred. nom.)girls (d.a.)</t>
         </is>
       </c>
       <c r="B516" t="inlineStr"/>
@@ -11259,7 +11143,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t xml:space="preserve">主/呼             puellae                 女孩（主语或谓语主格）/女孩（直接称呼）						</t>
         </is>
       </c>
       <c r="B517" t="inlineStr"/>
@@ -11280,7 +11164,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> Gen.              puellarum           of the girls</t>
         </is>
       </c>
       <c r="B518" t="inlineStr"/>
@@ -11301,7 +11185,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>• DRILL 2-3, PAGE 9, MAY NOW BE DONE</t>
+          <t>（介+离）</t>
         </is>
       </c>
       <c r="B519" t="inlineStr"/>
@@ -11322,7 +11206,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>Dat.                  puellis                to the girls/for the girls</t>
         </is>
       </c>
       <c r="B520" t="inlineStr"/>
@@ -11343,7 +11227,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>§4 Noun Morphology:Second Declension</t>
+          <t xml:space="preserve">A few prepositions can take either case,and </t>
         </is>
       </c>
       <c r="B521" t="inlineStr"/>
@@ -11364,7 +11248,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">Acc.                 puellas                the girls (d. O. ) </t>
         </is>
       </c>
       <c r="B522" t="inlineStr"/>
@@ -11385,7 +11269,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>their meanings differ according to which case they take.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr"/>
@@ -11406,7 +11290,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">Abl.                 puellis                 from the girls; by/with the girls; in the girls </t>
         </is>
       </c>
       <c r="B524" t="inlineStr"/>
@@ -11427,7 +11311,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Case Ending of the Secod Declension: Masculine/Feminine</t>
+          <t xml:space="preserve">&gt;ad takes the accusative and expresses motion to or toward a </t>
         </is>
       </c>
       <c r="B525" t="inlineStr"/>
@@ -11448,7 +11332,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">OBSERVATIONS </t>
         </is>
       </c>
       <c r="B526" t="inlineStr"/>
@@ -11469,7 +11353,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>注意</t>
         </is>
       </c>
       <c r="B527" t="inlineStr"/>
@@ -11490,7 +11374,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Nominative    -us/---6        -ī</t>
+          <t xml:space="preserve">1.The abbreviations for the case names used in the model declension above are standard and appear frequently in this book, as do the abbreviations subj.(subject), pred.nom.(predicate nominative), d. a.(direct address), and d. o.(direct object). </t>
         </is>
       </c>
       <c r="B528" t="inlineStr"/>
@@ -11511,7 +11395,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Genitive         -ī                 -ōrum</t>
+          <t>1.上例中的缩写将作为标准缩写在全书中频繁使用</t>
         </is>
       </c>
       <c r="B529" t="inlineStr"/>
@@ -11532,7 +11416,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Dative            -ō                -īs</t>
+          <t xml:space="preserve"> 2.In the first declension, as in most other declensions, the nominative and vocative endings in both singular and plural are identical and are therefore listed together. </t>
         </is>
       </c>
       <c r="B530" t="inlineStr"/>
@@ -11553,7 +11437,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Accusative     -um             -ōs</t>
+          <t>2.第一变格中，并且在大多数其余变格中，主格与呼格的单复数词尾均一致，故并列。</t>
         </is>
       </c>
       <c r="B531" t="inlineStr"/>
@@ -11574,7 +11458,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Ablative          -ō                -īs</t>
+          <t>2. 在大多数变格法（包括第一变格法）中，主格与呼格的单复数词尾均一致，故除非呼格与主格形式有异，否则词形变化表中不再列出呼格。</t>
         </is>
       </c>
       <c r="B532" t="inlineStr"/>
@@ -11595,7 +11479,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Vocative         -e                -ī</t>
+          <t xml:space="preserve">3.Certain endings of the first declension are used to mark more than one case: -ae = genitive singular, dative singular, and nominative/vocative plural; -is = dative plural and ablative plural. </t>
         </is>
       </c>
       <c r="B533" t="inlineStr"/>
@@ -11616,7 +11500,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>MEMORIZE THESE ENDINGS THROUGHLY, PROCEEDING FIRST DOWN THE SINGULAR COLUMN AND THEN DOWN THE PLURAL COLUMN。 BE PREPARED TO RECITE THE ENDINGS QUICKLY.</t>
+          <t>3.一些第一变格词尾用于标示多个格：-ae=属格单数，与格单数，主格/呼格复数；-is=与格复数，离格复数</t>
         </is>
       </c>
       <c r="B534" t="inlineStr"/>
@@ -11637,7 +11521,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">ALWAYS CONSIDER ALL POSSIBILITIES WHEN IDENTIFYING THE FORM OF A NOUN. </t>
         </is>
       </c>
       <c r="B535" t="inlineStr"/>
@@ -11658,7 +11542,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>To decline a masculine or feminine noun of the second declension, add these endings to the stem. For example:</t>
+          <t>谨记，在辨认名词形式时应考虑所有可能性</t>
         </is>
       </c>
       <c r="B536" t="inlineStr"/>
@@ -11679,7 +11563,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> Context usually makes clear which form occurs in a particular sentence. </t>
         </is>
       </c>
       <c r="B537" t="inlineStr"/>
@@ -11700,7 +11584,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t xml:space="preserve"> the meaning of ad with that of in (+acc.)in the diagram that follows.				</t>
+          <t>一般通过上下文便可以确定特定句子中出现的究竟是哪一形式</t>
         </is>
       </c>
       <c r="B538" t="inlineStr"/>
@@ -11721,7 +11605,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>stem=serv-</t>
+          <t xml:space="preserve"> 4. Two first-declension words in the vocabulary of this chapter, dea, deae f. , "goddess," and filia, filiae f. , "daughter," occasionally have irregular dative and ablative plural forms: deabus and filiabus, but these forms do not appear in this textbook. </t>
         </is>
       </c>
       <c r="B539" t="inlineStr"/>
@@ -11742,22 +11626,14 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Nom.</t>
+          <t>4.本章单词表中的dea, deae 阴, "女神" 和filia, filiae 阴 , "女儿"这两个第一-二变格名词偶有不规则与格和夺格：deabus与filiabus，但这些形式不会在本书中出现</t>
         </is>
       </c>
       <c r="B540" t="inlineStr"/>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>servus</t>
-        </is>
-      </c>
+      <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr"/>
-      <c r="F540" t="inlineStr">
-        <is>
-          <t>Singular</t>
-        </is>
-      </c>
+      <c r="F540" t="inlineStr"/>
       <c r="G540" t="inlineStr"/>
       <c r="H540" t="inlineStr"/>
       <c r="I540" t="inlineStr"/>
@@ -11771,22 +11647,14 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t xml:space="preserve"> 5.The Latin language has no definite article (the) and no indefinite article (a, an).  English definite or indefinite articles mav be freely added in translations of Latin nouns as context demands. </t>
         </is>
       </c>
       <c r="B541" t="inlineStr"/>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>servi</t>
-        </is>
-      </c>
+      <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr"/>
-      <c r="F541" t="inlineStr">
-        <is>
-          <t>a slave(subj. or pred. nom.)</t>
-        </is>
-      </c>
+      <c r="F541" t="inlineStr"/>
       <c r="G541" t="inlineStr"/>
       <c r="H541" t="inlineStr"/>
       <c r="I541" t="inlineStr"/>
@@ -11800,22 +11668,14 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>place. Compare</t>
         </is>
       </c>
       <c r="B542" t="inlineStr"/>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>servo</t>
-        </is>
-      </c>
+      <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
-      <c r="F542" t="inlineStr">
-        <is>
-          <t>of a slave</t>
-        </is>
-      </c>
+      <c r="F542" t="inlineStr"/>
       <c r="G542" t="inlineStr"/>
       <c r="H542" t="inlineStr"/>
       <c r="I542" t="inlineStr"/>
@@ -11827,16 +11687,16 @@
       <c r="O542" t="inlineStr"/>
     </row>
     <row r="543">
-      <c r="A543" t="inlineStr"/>
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>5. 拉丁语没有冠词，因此在翻译时需根据上下文语境判断名词所表示的含义究竟是“一个……”，还是“那个……”，亦或是单纯表示名词所指代的物体或概念，例如：拉丁语名词puella根据不同语境可译为“（有）一个女孩 (a girl)”、“这/那个女孩(the girl)”或“女孩(girl)”。</t>
+        </is>
+      </c>
       <c r="B543" t="inlineStr"/>
       <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr"/>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>to a slave/for a slave</t>
-        </is>
-      </c>
+      <c r="F543" t="inlineStr"/>
       <c r="G543" t="inlineStr"/>
       <c r="H543" t="inlineStr"/>
       <c r="I543" t="inlineStr"/>
@@ -11850,22 +11710,14 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t xml:space="preserve">Thus, the noun translated above as "the girl," "of the girl," etc. , could also be translated "a girl," "of a girl," etc. </t>
         </is>
       </c>
       <c r="B544" t="inlineStr"/>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>servum</t>
-        </is>
-      </c>
+      <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr">
-        <is>
-          <t>a slave(d.o.)</t>
-        </is>
-      </c>
+      <c r="F544" t="inlineStr"/>
       <c r="G544" t="inlineStr"/>
       <c r="H544" t="inlineStr"/>
       <c r="I544" t="inlineStr"/>
@@ -11877,24 +11729,12 @@
       <c r="O544" t="inlineStr"/>
     </row>
     <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>【表格】</t>
-        </is>
-      </c>
+      <c r="A545" t="inlineStr"/>
       <c r="B545" t="inlineStr"/>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>servo</t>
-        </is>
-      </c>
+      <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr"/>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>from a slaver; by/with a slave; in a slave</t>
-        </is>
-      </c>
+      <c r="F545" t="inlineStr"/>
       <c r="G545" t="inlineStr"/>
       <c r="H545" t="inlineStr"/>
       <c r="I545" t="inlineStr"/>
@@ -11908,22 +11748,14 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Voc.</t>
+          <t xml:space="preserve"> Sometimes it is appropriate to use no article: "money" or "of books. </t>
         </is>
       </c>
       <c r="B546" t="inlineStr"/>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>serve</t>
-        </is>
-      </c>
+      <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr"/>
-      <c r="F546" t="inlineStr">
-        <is>
-          <t>slave(d.a.)</t>
-        </is>
-      </c>
+      <c r="F546" t="inlineStr"/>
       <c r="G546" t="inlineStr"/>
       <c r="H546" t="inlineStr"/>
       <c r="I546" t="inlineStr"/>
@@ -11940,11 +11772,7 @@
       <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr"/>
-      <c r="F547" t="inlineStr">
-        <is>
-          <t>Plural</t>
-        </is>
-      </c>
+      <c r="F547" t="inlineStr"/>
       <c r="G547" t="inlineStr"/>
       <c r="H547" t="inlineStr"/>
       <c r="I547" t="inlineStr"/>
@@ -11958,22 +11786,14 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t xml:space="preserve">Although there are words in Latin for "his," "her," and "their," possessive adjectives such as these are often omitted in Latin. They may be freely added in English translations. </t>
         </is>
       </c>
       <c r="B548" t="inlineStr"/>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>servi</t>
-        </is>
-      </c>
+      <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr"/>
-      <c r="F548" t="inlineStr">
-        <is>
-          <t>slaves(subj. or pred. nom.)</t>
-        </is>
-      </c>
+      <c r="F548" t="inlineStr"/>
       <c r="G548" t="inlineStr"/>
       <c r="H548" t="inlineStr"/>
       <c r="I548" t="inlineStr"/>
@@ -11985,16 +11805,16 @@
       <c r="O548" t="inlineStr"/>
     </row>
     <row r="549">
-      <c r="A549" t="inlineStr"/>
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>虽然拉丁语中有对应“他的”“她的”“他们的”的单词，但我们常常省略这些所有格形容词。翻译时可自由选择添加与否。</t>
+        </is>
+      </c>
       <c r="B549" t="inlineStr"/>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr"/>
-      <c r="F549" t="inlineStr">
-        <is>
-          <t>slaves(d.a.)</t>
-        </is>
-      </c>
+      <c r="F549" t="inlineStr"/>
       <c r="G549" t="inlineStr"/>
       <c r="H549" t="inlineStr"/>
       <c r="I549" t="inlineStr"/>
@@ -12008,22 +11828,14 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>• DRILL 2-3, PAGE 9, MAY NOW BE DONE</t>
         </is>
       </c>
       <c r="B550" t="inlineStr"/>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>servorum</t>
-        </is>
-      </c>
+      <c r="C550" t="inlineStr"/>
       <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr"/>
-      <c r="F550" t="inlineStr">
-        <is>
-          <t>of slaves</t>
-        </is>
-      </c>
+      <c r="F550" t="inlineStr"/>
       <c r="G550" t="inlineStr"/>
       <c r="H550" t="inlineStr"/>
       <c r="I550" t="inlineStr"/>
@@ -12035,24 +11847,12 @@
       <c r="O550" t="inlineStr"/>
     </row>
     <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>【表格】</t>
-        </is>
-      </c>
+      <c r="A551" t="inlineStr"/>
       <c r="B551" t="inlineStr"/>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>servis</t>
-        </is>
-      </c>
+      <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr"/>
-      <c r="F551" t="inlineStr">
-        <is>
-          <t>to slaves/for slaves</t>
-        </is>
-      </c>
+      <c r="F551" t="inlineStr"/>
       <c r="G551" t="inlineStr"/>
       <c r="H551" t="inlineStr"/>
       <c r="I551" t="inlineStr"/>
@@ -12066,22 +11866,14 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>序号53，页数21（拆分：？，？）（机翻：？，？）（人翻：？，？）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
         </is>
       </c>
       <c r="B552" t="inlineStr"/>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>servos</t>
-        </is>
-      </c>
+      <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr"/>
-      <c r="F552" t="inlineStr">
-        <is>
-          <t>slaves(d.o.)</t>
-        </is>
-      </c>
+      <c r="F552" t="inlineStr"/>
       <c r="G552" t="inlineStr"/>
       <c r="H552" t="inlineStr"/>
       <c r="I552" t="inlineStr"/>
@@ -12093,24 +11885,12 @@
       <c r="O552" t="inlineStr"/>
     </row>
     <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>【表格】</t>
-        </is>
-      </c>
+      <c r="A553" t="inlineStr"/>
       <c r="B553" t="inlineStr"/>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>servis</t>
-        </is>
-      </c>
+      <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr"/>
-      <c r="F553" t="inlineStr">
-        <is>
-          <t>from slaves; by/with slaves; in slaves</t>
-        </is>
-      </c>
+      <c r="F553" t="inlineStr"/>
       <c r="G553" t="inlineStr"/>
       <c r="H553" t="inlineStr"/>
       <c r="I553" t="inlineStr"/>
@@ -12124,7 +11904,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t xml:space="preserve">6. Most masculin and feminine nouns of the second declension use -us as the nominative singular ending. </t>
+          <t>§4 Noun Morphology:Second Declension</t>
         </is>
       </c>
       <c r="B554" t="inlineStr"/>
@@ -12145,7 +11925,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>§4 名词词法：第二变格</t>
         </is>
       </c>
       <c r="B555" t="inlineStr"/>
@@ -12166,7 +11946,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>Gender Note: Most nous of the second declension are masculine, some are feminine. and many are neuter with endings slightly different from masculine and feminine nouns.</t>
         </is>
       </c>
       <c r="B556" t="inlineStr"/>
@@ -12187,7 +11967,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>关于性：第二变格名词中绝大多数都是阳性，一些是阴性，还有许多词尾与前两者略有不同的中性</t>
         </is>
       </c>
       <c r="B557" t="inlineStr"/>
@@ -12208,7 +11988,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Case Ending of the Secod Declension: Masculine/Feminine</t>
         </is>
       </c>
       <c r="B558" t="inlineStr"/>
@@ -12229,7 +12009,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>第二变格格尾：阳性/阴性</t>
         </is>
       </c>
       <c r="B559" t="inlineStr"/>
@@ -12250,7 +12030,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>OBSERVATIONS</t>
+          <t xml:space="preserve">                     Singular     Plural</t>
         </is>
       </c>
       <c r="B560" t="inlineStr"/>
@@ -12271,7 +12051,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Nominative    -us/---6        -ī</t>
         </is>
       </c>
       <c r="B561" t="inlineStr"/>
@@ -12292,7 +12072,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Certain endings for masculine/feminine nouns of the second declension are used to mark more than one case: -i = genitive singular and nominative/vocative plural; -ö = dative singular and ablative singular; -is = dative plural and ablative plural. </t>
+          <t>Genitive         -ī                 -ōrum</t>
         </is>
       </c>
       <c r="B562" t="inlineStr"/>
@@ -12313,7 +12093,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Dative            -ō                -īs</t>
         </is>
       </c>
       <c r="B563" t="inlineStr"/>
@@ -12334,7 +12114,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AIWAYS CONSIDER ALL POSSIBILITIES WHEN IDENTIFYING THE FORM OF A NOUN. </t>
+          <t>Accusative     -um             -ōs</t>
         </is>
       </c>
       <c r="B564" t="inlineStr"/>
@@ -12355,7 +12135,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Ablative          -ō                -īs</t>
         </is>
       </c>
       <c r="B565" t="inlineStr"/>
@@ -12376,7 +12156,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context usually makes clear which form appears in a particular sentence. </t>
+          <t>Vocative         -e                -ī</t>
         </is>
       </c>
       <c r="B566" t="inlineStr"/>
@@ -12395,11 +12175,7 @@
       <c r="O566" t="inlineStr"/>
     </row>
     <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A567" t="inlineStr"/>
       <c r="B567" t="inlineStr"/>
       <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr"/>
@@ -12418,7 +12194,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.Many endings of the second declension are either similar to or identical with corresponding endings of the first declension. </t>
+          <t>MEMORIZE THESE ENDINGS THROUGHLY, PROCEEDING FIRST DOWN THE SINGULAR COLUMN AND THEN DOWN THE PLURAL COLUMN。 BE PREPARED TO RECITE THE ENDINGS QUICKLY.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr"/>
@@ -12439,7 +12215,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>谨记，牢记这些词尾，按列先后记住单数与复数。要能够快速复述它们。</t>
         </is>
       </c>
       <c r="B569" t="inlineStr"/>
@@ -12460,7 +12236,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>To decline a masculine or feminine noun of the second declension, add these endings to the stem. For example:</t>
         </is>
       </c>
       <c r="B570" t="inlineStr"/>
@@ -12481,7 +12257,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>通过在词干上添加下列词尾来对第二变格阳性/阴性名词进行变格。例如：</t>
         </is>
       </c>
       <c r="B571" t="inlineStr"/>
@@ -12502,7 +12278,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.Second-declension nouns whose stems end in -i have two possible forms for the genitive singular, one a contraction of the other.  For example: </t>
+          <t xml:space="preserve"> the meaning of ad with that of in (+acc.)in the diagram that follows.				</t>
         </is>
       </c>
       <c r="B572" t="inlineStr"/>
@@ -12523,7 +12299,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>stem=serv-</t>
         </is>
       </c>
       <c r="B573" t="inlineStr"/>
@@ -12542,11 +12318,7 @@
       <c r="O573" t="inlineStr"/>
     </row>
     <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>gladius, gladii or gladi m. sword</t>
-        </is>
-      </c>
+      <c r="A574" t="inlineStr"/>
       <c r="B574" t="inlineStr"/>
       <c r="C574" t="inlineStr"/>
       <c r="D574" t="inlineStr"/>
@@ -12565,14 +12337,22 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Nom.</t>
         </is>
       </c>
       <c r="B575" t="inlineStr"/>
-      <c r="C575" t="inlineStr"/>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>servus</t>
+        </is>
+      </c>
       <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr"/>
-      <c r="F575" t="inlineStr"/>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Singular</t>
+        </is>
+      </c>
       <c r="G575" t="inlineStr"/>
       <c r="H575" t="inlineStr"/>
       <c r="I575" t="inlineStr"/>
@@ -12586,14 +12366,22 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>Gen.</t>
         </is>
       </c>
       <c r="B576" t="inlineStr"/>
-      <c r="C576" t="inlineStr"/>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>servi</t>
+        </is>
+      </c>
       <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr"/>
-      <c r="F576" t="inlineStr"/>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>a slave(subj. or pred. nom.)</t>
+        </is>
+      </c>
       <c r="G576" t="inlineStr"/>
       <c r="H576" t="inlineStr"/>
       <c r="I576" t="inlineStr"/>
@@ -12607,14 +12395,22 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Dat.</t>
         </is>
       </c>
       <c r="B577" t="inlineStr"/>
-      <c r="C577" t="inlineStr"/>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>servo</t>
+        </is>
+      </c>
       <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr"/>
-      <c r="F577" t="inlineStr"/>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>of a slave</t>
+        </is>
+      </c>
       <c r="G577" t="inlineStr"/>
       <c r="H577" t="inlineStr"/>
       <c r="I577" t="inlineStr"/>
@@ -12626,16 +12422,16 @@
       <c r="O577" t="inlineStr"/>
     </row>
     <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.The second declension is the only declension in which the vocative differs from the nominative, and it does so only in the singular for masculine/feminine nouns. </t>
-        </is>
-      </c>
+      <c r="A578" t="inlineStr"/>
       <c r="B578" t="inlineStr"/>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr"/>
-      <c r="F578" t="inlineStr"/>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>to a slave/for a slave</t>
+        </is>
+      </c>
       <c r="G578" t="inlineStr"/>
       <c r="H578" t="inlineStr"/>
       <c r="I578" t="inlineStr"/>
@@ -12649,14 +12445,22 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Acc.</t>
         </is>
       </c>
       <c r="B579" t="inlineStr"/>
-      <c r="C579" t="inlineStr"/>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>servum</t>
+        </is>
+      </c>
       <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr"/>
-      <c r="F579" t="inlineStr"/>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>a slave(d.o.)</t>
+        </is>
+      </c>
       <c r="G579" t="inlineStr"/>
       <c r="H579" t="inlineStr"/>
       <c r="I579" t="inlineStr"/>
@@ -12670,14 +12474,22 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>Abl.</t>
         </is>
       </c>
       <c r="B580" t="inlineStr"/>
-      <c r="C580" t="inlineStr"/>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>servo</t>
+        </is>
+      </c>
       <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr"/>
-      <c r="F580" t="inlineStr"/>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>from a slaver; by/with a slave; in a slave</t>
+        </is>
+      </c>
       <c r="G580" t="inlineStr"/>
       <c r="H580" t="inlineStr"/>
       <c r="I580" t="inlineStr"/>
@@ -12691,14 +12503,22 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Voc.</t>
         </is>
       </c>
       <c r="B581" t="inlineStr"/>
-      <c r="C581" t="inlineStr"/>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>serve</t>
+        </is>
+      </c>
       <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr"/>
-      <c r="F581" t="inlineStr"/>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>slave(d.a.)</t>
+        </is>
+      </c>
       <c r="G581" t="inlineStr"/>
       <c r="H581" t="inlineStr"/>
       <c r="I581" t="inlineStr"/>
@@ -12710,16 +12530,16 @@
       <c r="O581" t="inlineStr"/>
     </row>
     <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A582" t="inlineStr"/>
       <c r="B582" t="inlineStr"/>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr"/>
-      <c r="F582" t="inlineStr"/>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Plural</t>
+        </is>
+      </c>
       <c r="G582" t="inlineStr"/>
       <c r="H582" t="inlineStr"/>
       <c r="I582" t="inlineStr"/>
@@ -12733,14 +12553,22 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Nom./Voc.</t>
         </is>
       </c>
       <c r="B583" t="inlineStr"/>
-      <c r="C583" t="inlineStr"/>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>servi</t>
+        </is>
+      </c>
       <c r="D583" t="inlineStr"/>
       <c r="E583" t="inlineStr"/>
-      <c r="F583" t="inlineStr"/>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>slaves(subj. or pred. nom.)</t>
+        </is>
+      </c>
       <c r="G583" t="inlineStr"/>
       <c r="H583" t="inlineStr"/>
       <c r="I583" t="inlineStr"/>
@@ -12752,16 +12580,16 @@
       <c r="O583" t="inlineStr"/>
     </row>
     <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> For other masculine and feminine nouns of this declension, the vocative singular is identical with the nominative singular.  For example:</t>
-        </is>
-      </c>
+      <c r="A584" t="inlineStr"/>
       <c r="B584" t="inlineStr"/>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr"/>
       <c r="E584" t="inlineStr"/>
-      <c r="F584" t="inlineStr"/>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>slaves(d.a.)</t>
+        </is>
+      </c>
       <c r="G584" t="inlineStr"/>
       <c r="H584" t="inlineStr"/>
       <c r="I584" t="inlineStr"/>
@@ -12775,14 +12603,22 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Gen.</t>
         </is>
       </c>
       <c r="B585" t="inlineStr"/>
-      <c r="C585" t="inlineStr"/>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>servorum</t>
+        </is>
+      </c>
       <c r="D585" t="inlineStr"/>
       <c r="E585" t="inlineStr"/>
-      <c r="F585" t="inlineStr"/>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>of slaves</t>
+        </is>
+      </c>
       <c r="G585" t="inlineStr"/>
       <c r="H585" t="inlineStr"/>
       <c r="I585" t="inlineStr"/>
@@ -12796,14 +12632,22 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t xml:space="preserve">servus vocative singular = serve </t>
+          <t>Dat.</t>
         </is>
       </c>
       <c r="B586" t="inlineStr"/>
-      <c r="C586" t="inlineStr"/>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>servis</t>
+        </is>
+      </c>
       <c r="D586" t="inlineStr"/>
       <c r="E586" t="inlineStr"/>
-      <c r="F586" t="inlineStr"/>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>to slaves/for slaves</t>
+        </is>
+      </c>
       <c r="G586" t="inlineStr"/>
       <c r="H586" t="inlineStr"/>
       <c r="I586" t="inlineStr"/>
@@ -12817,14 +12661,22 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t xml:space="preserve">filius vocative singular = fili </t>
+          <t>Acc.</t>
         </is>
       </c>
       <c r="B587" t="inlineStr"/>
-      <c r="C587" t="inlineStr"/>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>servos</t>
+        </is>
+      </c>
       <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr"/>
-      <c r="F587" t="inlineStr"/>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>slaves(d.o.)</t>
+        </is>
+      </c>
       <c r="G587" t="inlineStr"/>
       <c r="H587" t="inlineStr"/>
       <c r="I587" t="inlineStr"/>
@@ -12838,14 +12690,22 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>Abl.</t>
         </is>
       </c>
       <c r="B588" t="inlineStr"/>
-      <c r="C588" t="inlineStr"/>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>servis</t>
+        </is>
+      </c>
       <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr"/>
-      <c r="F588" t="inlineStr"/>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>from slaves; by/with slaves; in slaves</t>
+        </is>
+      </c>
       <c r="G588" t="inlineStr"/>
       <c r="H588" t="inlineStr"/>
       <c r="I588" t="inlineStr"/>
@@ -12857,11 +12717,7 @@
       <c r="O588" t="inlineStr"/>
     </row>
     <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5. Every vocative plural is identical with the nominative plural in all declensions. </t>
-        </is>
-      </c>
+      <c r="A589" t="inlineStr"/>
       <c r="B589" t="inlineStr"/>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr"/>
@@ -12880,7 +12736,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">6. Most masculin and feminine nouns of the second declension use -us as the nominative singular ending. </t>
         </is>
       </c>
       <c r="B590" t="inlineStr"/>
@@ -12901,7 +12757,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>6.绝大多数阳性与阴性第二变格名词的主格单数词尾是-us</t>
         </is>
       </c>
       <c r="B591" t="inlineStr"/>
@@ -12922,7 +12778,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>As is clear from the vocabulary entries, however, a number of nouns lack any nominative singular ending and instead use a form of the stem of the noun as the nominative singular form. Thus, servus, suervi m.slave, but puer, pueri m. boy and liber, libri m. book.</t>
         </is>
       </c>
       <c r="B592" t="inlineStr"/>
@@ -12943,7 +12799,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t xml:space="preserve">Case Endings of the Second Declension: Neuter </t>
+          <t>然而，单词表中明显有些单词以词干的一种形式代替了其主格单数词尾，因此servus, suervi m.（奴隶）是这样, 但是 puer, pueri m. （男孩） 与liber, libri m.（书）.则是这样。</t>
         </is>
       </c>
       <c r="B593" t="inlineStr"/>
@@ -12964,7 +12820,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>但毫无疑问单词表中明显有相当一部分单词缺少单数主格词尾，并且单数主格是其词干的某种形式，因此第二变格法既有像servus, suervi（m. 奴隶）这样的名词, 也有诸如puer, pueri（m. 男孩） 和liber, libri（m. 书）的名词。</t>
         </is>
       </c>
       <c r="B594" t="inlineStr"/>
@@ -12985,7 +12841,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>序号54，页数22（拆分：？，？）（机翻：？，？）（人翻：？，？）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
         </is>
       </c>
       <c r="B595" t="inlineStr"/>
@@ -13004,11 +12860,7 @@
       <c r="O595" t="inlineStr"/>
     </row>
     <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Nominative/Vocative     -um                        -a </t>
-        </is>
-      </c>
+      <c r="A596" t="inlineStr"/>
       <c r="B596" t="inlineStr"/>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr"/>
@@ -13027,7 +12879,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genitive                          -i                           -ōrum </t>
+          <t>OBSERVATIONS</t>
         </is>
       </c>
       <c r="B597" t="inlineStr"/>
@@ -13048,7 +12900,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Dative                            -ō                           -īs</t>
+          <t>注意</t>
         </is>
       </c>
       <c r="B598" t="inlineStr"/>
@@ -13069,7 +12921,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Accusative                    -um                        -a </t>
+          <t xml:space="preserve">1.Certain endings for masculine/feminine nouns of the second declension are used to mark more than one case: -i = genitive singular and nominative/vocative plural; -ö = dative singular and ablative singular; -is = dative plural and ablative plural. </t>
         </is>
       </c>
       <c r="B599" t="inlineStr"/>
@@ -13090,7 +12942,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ablative                          -ō                           -īs </t>
+          <t>1一些阳性/阴性第二变格词尾用于表示多个格：-i=属格单数，主格/呼格复数；-o=与格单数，离格单数；-is=与格复数，离格单数</t>
         </is>
       </c>
       <c r="B600" t="inlineStr"/>
@@ -13111,7 +12963,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>MEMORIZE THESE ENDINGS THOROUGHIY, PROCEEDING FIRST DOWN THE SINGULAR COLUMN AND THEN DOWN THE PLURAL COLUMN.  BE PREPARED TO RECITE THE ENDINGS QUICKLY</t>
+          <t xml:space="preserve"> AIWAYS CONSIDER ALL POSSIBILITIES WHEN IDENTIFYING THE FORM OF A NOUN. </t>
         </is>
       </c>
       <c r="B601" t="inlineStr"/>
@@ -13132,7 +12984,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>谨记，在辨认名词形式时应考虑所有可能性</t>
         </is>
       </c>
       <c r="B602" t="inlineStr"/>
@@ -13153,7 +13005,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t xml:space="preserve"> Context usually makes clear which form appears in a particular sentence. </t>
         </is>
       </c>
       <c r="B603" t="inlineStr"/>
@@ -13174,7 +13026,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t xml:space="preserve">To decline a neuter noun of the second declension, add these endings to the stem.  For example: </t>
+          <t>一般通过上下文便可以确定特定句子中出现的究竟是哪一形式</t>
         </is>
       </c>
       <c r="B604" t="inlineStr"/>
@@ -13195,7 +13047,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">2.Many endings of the second declension are either similar to or identical with corresponding endings of the first declension. </t>
         </is>
       </c>
       <c r="B605" t="inlineStr"/>
@@ -13216,7 +13068,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>2.许多第二变格词尾与第一变格的对应词尾相似或相同</t>
         </is>
       </c>
       <c r="B606" t="inlineStr"/>
@@ -13237,7 +13089,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>stem = pericul-</t>
+          <t xml:space="preserve"> Compare accusative singular -um to -am; genitive plural -örum to ārum; dative and ablative plural -is to -is; and accusative plural -ôs to -ãs. </t>
         </is>
       </c>
       <c r="B607" t="inlineStr"/>
@@ -13258,7 +13110,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                            Singular </t>
+          <t>宾格单数-um与-am相似；属格复数-orum与-arum相似；与格复数相同，均为-is；宾格复数-os与-as相似</t>
         </is>
       </c>
       <c r="B608" t="inlineStr"/>
@@ -13279,7 +13131,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nom. /Voc.              periculum             danger (subj.  or pred.  nom. ) danger (d. a. </t>
+          <t xml:space="preserve">3.Second-declension nouns whose stems end in -i have two possible forms for the genitive singular, one a contraction of the other.  For example: </t>
         </is>
       </c>
       <c r="B609" t="inlineStr"/>
@@ -13300,7 +13152,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>3.第二变格中词干以-i结尾的名词有两种属格单数形式，例如：</t>
         </is>
       </c>
       <c r="B610" t="inlineStr"/>
@@ -13321,7 +13173,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>gladius, gladii or gladi m. sword</t>
         </is>
       </c>
       <c r="B611" t="inlineStr"/>
@@ -13342,7 +13194,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>gladius, gladii 或 gladi 阳，剑</t>
         </is>
       </c>
       <c r="B612" t="inlineStr"/>
@@ -13363,7 +13215,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t xml:space="preserve">In the second form, the short -i of the stem has contracted with the -i of the ending.  This shortened form of the genitive singular is not given in the vocabulary entry for nouns whose stems end in -i, but it appears in drills, sentences, and readings. </t>
         </is>
       </c>
       <c r="B613" t="inlineStr"/>
@@ -13384,7 +13236,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                            Plural </t>
+          <t>-que是个</t>
         </is>
       </c>
       <c r="B614" t="inlineStr"/>
@@ -13405,7 +13257,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nom. /Voc.           pericula                       dangers (subj.  or pred.  nom. ) </t>
+          <t xml:space="preserve">4.The second declension is the only declension in which the vocative differs from the nominative, and it does so only in the singular for masculine/feminine nouns. </t>
         </is>
       </c>
       <c r="B615" t="inlineStr"/>
@@ -13426,7 +13278,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                               dangers (d. a. </t>
+          <t>4.第二变格是唯一一个呼格与主格不一致的变格（仅阳性/阴性名词单数时不同）</t>
         </is>
       </c>
       <c r="B616" t="inlineStr"/>
@@ -13447,7 +13299,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t xml:space="preserve"> For nouns whose nominative singular ending is -us, the vocative singular ending is -e. </t>
         </is>
       </c>
       <c r="B617" t="inlineStr"/>
@@ -13468,7 +13320,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>主格单数词尾是-us的名词，呼格单数结尾为-e</t>
         </is>
       </c>
       <c r="B618" t="inlineStr"/>
@@ -13489,7 +13341,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t xml:space="preserve"> For the noun filius and proper names of the second declension whose nominative singular ending is -ius, the vocative singular ending is -i. </t>
         </is>
       </c>
       <c r="B619" t="inlineStr"/>
@@ -13510,7 +13362,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>像filius和专有名词这样以-ius作为主格单数词尾的第二变格名词，呼格单数为-i</t>
         </is>
       </c>
       <c r="B620" t="inlineStr"/>
@@ -13531,7 +13383,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t xml:space="preserve"> OBSERVATIONS</t>
+          <t xml:space="preserve"> For other masculine and feminine nouns of this declension, the vocative singular is identical with the nominative singular.  For example:</t>
         </is>
       </c>
       <c r="B621" t="inlineStr"/>
@@ -13552,7 +13404,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>【表格译文】</t>
+          <t>其余第二变格阳性/阴性名词的呼格与主格一致</t>
         </is>
       </c>
       <c r="B622" t="inlineStr"/>
@@ -13573,7 +13425,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Most of the endings for neuter nouns of the second declension are identical with the endings for masculine/feminine second-declension nouns. </t>
+          <t xml:space="preserve">servus vocative singular = serve </t>
         </is>
       </c>
       <c r="B623" t="inlineStr"/>
@@ -13594,7 +13446,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">filius vocative singular = fili </t>
         </is>
       </c>
       <c r="B624" t="inlineStr"/>
@@ -13615,7 +13467,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Neuter nouns differ only in having -um in the nominative and vocative singular and -a in the nominative, vocative, and accusative plural. </t>
+          <t xml:space="preserve">puer vocative singular = puer </t>
         </is>
       </c>
       <c r="B625" t="inlineStr"/>
@@ -13634,11 +13486,7 @@
       <c r="O625" t="inlineStr"/>
     </row>
     <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A626" t="inlineStr"/>
       <c r="B626" t="inlineStr"/>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr"/>
@@ -13657,7 +13505,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALL NEUTER WORDS IN LATIN HAVE IDENTICAL NOMINATIVE AND ACCUSATIVE FORMS IN BOTH THE SINGULAR AND THE PLURAL. </t>
+          <t xml:space="preserve">5. Every vocative plural is identical with the nominative plural in all declensions. </t>
         </is>
       </c>
       <c r="B627" t="inlineStr"/>
@@ -13678,7 +13526,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>5.所有变格的呼格复数都与主格复数一致。</t>
         </is>
       </c>
       <c r="B628" t="inlineStr"/>
@@ -13699,7 +13547,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>2. As is true for masculine/feminine second-declension nouns, neuter nouns whose stems end in -i have two possible forms for the genitive singular, one a contraction of the other.  For example:</t>
+          <t>6. The noun deus, dei m.  has certain irregular forms in the plural: di (nom. /voc.  pl. ), deum (gen.  pl. ), and dis (dat. /abl.  pl. ).  For the full declension of this noun see the vocabulary note on p.  12.</t>
         </is>
       </c>
       <c r="B629" t="inlineStr"/>
@@ -13720,7 +13568,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>6.名词deus, dei 阳，有着不规则的复数形式:di(主格/呼格复数)，deum（属格复数），dis（与格/离格复数）。这一名词的全变格见单词表（12页）</t>
         </is>
       </c>
       <c r="B630" t="inlineStr"/>
@@ -13741,7 +13589,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t xml:space="preserve">                               consilium, consilii or consili n.  plan, advice; judgment </t>
+          <t xml:space="preserve">Case Endings of the Second Declension: Neuter </t>
         </is>
       </c>
       <c r="B631" t="inlineStr"/>
@@ -13762,7 +13610,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>第二变格格尾：中性</t>
         </is>
       </c>
       <c r="B632" t="inlineStr"/>
@@ -13783,7 +13631,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>• DRILL 4, PAGE 15, MAY NOW BE DONE</t>
+          <t>附言连词。</t>
         </is>
       </c>
       <c r="B633" t="inlineStr"/>
@@ -13804,7 +13652,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve"> Nominative/Vocative     -um                        -a </t>
         </is>
       </c>
       <c r="B634" t="inlineStr"/>
@@ -13825,7 +13673,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t xml:space="preserve">Genitive                          -i                           -ōrum </t>
         </is>
       </c>
       <c r="B635" t="inlineStr"/>
@@ -13846,7 +13694,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>Dative                            -ō                           -īs</t>
         </is>
       </c>
       <c r="B636" t="inlineStr"/>
@@ -13864,6 +13712,889 @@
       <c r="N636" t="inlineStr"/>
       <c r="O636" t="inlineStr"/>
     </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Accusative                    -um                        -a </t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr"/>
+      <c r="C637" t="inlineStr"/>
+      <c r="D637" t="inlineStr"/>
+      <c r="E637" t="inlineStr"/>
+      <c r="F637" t="inlineStr"/>
+      <c r="G637" t="inlineStr"/>
+      <c r="H637" t="inlineStr"/>
+      <c r="I637" t="inlineStr"/>
+      <c r="J637" t="inlineStr"/>
+      <c r="K637" t="inlineStr"/>
+      <c r="L637" t="inlineStr"/>
+      <c r="M637" t="inlineStr"/>
+      <c r="N637" t="inlineStr"/>
+      <c r="O637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ablative                          -ō                           -īs </t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr"/>
+      <c r="C638" t="inlineStr"/>
+      <c r="D638" t="inlineStr"/>
+      <c r="E638" t="inlineStr"/>
+      <c r="F638" t="inlineStr"/>
+      <c r="G638" t="inlineStr"/>
+      <c r="H638" t="inlineStr"/>
+      <c r="I638" t="inlineStr"/>
+      <c r="J638" t="inlineStr"/>
+      <c r="K638" t="inlineStr"/>
+      <c r="L638" t="inlineStr"/>
+      <c r="M638" t="inlineStr"/>
+      <c r="N638" t="inlineStr"/>
+      <c r="O638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr"/>
+      <c r="B639" t="inlineStr"/>
+      <c r="C639" t="inlineStr"/>
+      <c r="D639" t="inlineStr"/>
+      <c r="E639" t="inlineStr"/>
+      <c r="F639" t="inlineStr"/>
+      <c r="G639" t="inlineStr"/>
+      <c r="H639" t="inlineStr"/>
+      <c r="I639" t="inlineStr"/>
+      <c r="J639" t="inlineStr"/>
+      <c r="K639" t="inlineStr"/>
+      <c r="L639" t="inlineStr"/>
+      <c r="M639" t="inlineStr"/>
+      <c r="N639" t="inlineStr"/>
+      <c r="O639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>MEMORIZE THESE ENDINGS THOROUGHIY, PROCEEDING FIRST DOWN THE SINGULAR COLUMN AND THEN DOWN THE PLURAL COLUMN.  BE PREPARED TO RECITE THE ENDINGS QUICKLY</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr"/>
+      <c r="C640" t="inlineStr"/>
+      <c r="D640" t="inlineStr"/>
+      <c r="E640" t="inlineStr"/>
+      <c r="F640" t="inlineStr"/>
+      <c r="G640" t="inlineStr"/>
+      <c r="H640" t="inlineStr"/>
+      <c r="I640" t="inlineStr"/>
+      <c r="J640" t="inlineStr"/>
+      <c r="K640" t="inlineStr"/>
+      <c r="L640" t="inlineStr"/>
+      <c r="M640" t="inlineStr"/>
+      <c r="N640" t="inlineStr"/>
+      <c r="O640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>谨记，牢记这些词尾，按列先后记住单数与复数。要能够快速复述它们。</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr"/>
+      <c r="C641" t="inlineStr"/>
+      <c r="D641" t="inlineStr"/>
+      <c r="E641" t="inlineStr"/>
+      <c r="F641" t="inlineStr"/>
+      <c r="G641" t="inlineStr"/>
+      <c r="H641" t="inlineStr"/>
+      <c r="I641" t="inlineStr"/>
+      <c r="J641" t="inlineStr"/>
+      <c r="K641" t="inlineStr"/>
+      <c r="L641" t="inlineStr"/>
+      <c r="M641" t="inlineStr"/>
+      <c r="N641" t="inlineStr"/>
+      <c r="O641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>序号55，页数23（拆分：？，？）（机翻：？，？）（人翻：？，？）（润色（按句）：？，？）（校对：？，？）（附加评论/修改建议：？，？）</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr"/>
+      <c r="C642" t="inlineStr"/>
+      <c r="D642" t="inlineStr"/>
+      <c r="E642" t="inlineStr"/>
+      <c r="F642" t="inlineStr"/>
+      <c r="G642" t="inlineStr"/>
+      <c r="H642" t="inlineStr"/>
+      <c r="I642" t="inlineStr"/>
+      <c r="J642" t="inlineStr"/>
+      <c r="K642" t="inlineStr"/>
+      <c r="L642" t="inlineStr"/>
+      <c r="M642" t="inlineStr"/>
+      <c r="N642" t="inlineStr"/>
+      <c r="O642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr"/>
+      <c r="B643" t="inlineStr"/>
+      <c r="C643" t="inlineStr"/>
+      <c r="D643" t="inlineStr"/>
+      <c r="E643" t="inlineStr"/>
+      <c r="F643" t="inlineStr"/>
+      <c r="G643" t="inlineStr"/>
+      <c r="H643" t="inlineStr"/>
+      <c r="I643" t="inlineStr"/>
+      <c r="J643" t="inlineStr"/>
+      <c r="K643" t="inlineStr"/>
+      <c r="L643" t="inlineStr"/>
+      <c r="M643" t="inlineStr"/>
+      <c r="N643" t="inlineStr"/>
+      <c r="O643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To decline a neuter noun of the second declension, add these endings to the stem.  For example: </t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr"/>
+      <c r="C644" t="inlineStr"/>
+      <c r="D644" t="inlineStr"/>
+      <c r="E644" t="inlineStr"/>
+      <c r="F644" t="inlineStr"/>
+      <c r="G644" t="inlineStr"/>
+      <c r="H644" t="inlineStr"/>
+      <c r="I644" t="inlineStr"/>
+      <c r="J644" t="inlineStr"/>
+      <c r="K644" t="inlineStr"/>
+      <c r="L644" t="inlineStr"/>
+      <c r="M644" t="inlineStr"/>
+      <c r="N644" t="inlineStr"/>
+      <c r="O644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>通过在词干上添加下列词尾来对第二变格中性名词进行变格。例如：</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr"/>
+      <c r="C645" t="inlineStr"/>
+      <c r="D645" t="inlineStr"/>
+      <c r="E645" t="inlineStr"/>
+      <c r="F645" t="inlineStr"/>
+      <c r="G645" t="inlineStr"/>
+      <c r="H645" t="inlineStr"/>
+      <c r="I645" t="inlineStr"/>
+      <c r="J645" t="inlineStr"/>
+      <c r="K645" t="inlineStr"/>
+      <c r="L645" t="inlineStr"/>
+      <c r="M645" t="inlineStr"/>
+      <c r="N645" t="inlineStr"/>
+      <c r="O645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>enclitic来源于希腊语动词enklino（lean on），一个附言连词直接附着在它的前一个单词上。</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr"/>
+      <c r="C646" t="inlineStr"/>
+      <c r="D646" t="inlineStr"/>
+      <c r="E646" t="inlineStr"/>
+      <c r="F646" t="inlineStr"/>
+      <c r="G646" t="inlineStr"/>
+      <c r="H646" t="inlineStr"/>
+      <c r="I646" t="inlineStr"/>
+      <c r="J646" t="inlineStr"/>
+      <c r="K646" t="inlineStr"/>
+      <c r="L646" t="inlineStr"/>
+      <c r="M646" t="inlineStr"/>
+      <c r="N646" t="inlineStr"/>
+      <c r="O646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>stem = pericul-</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr"/>
+      <c r="C647" t="inlineStr"/>
+      <c r="D647" t="inlineStr"/>
+      <c r="E647" t="inlineStr"/>
+      <c r="F647" t="inlineStr"/>
+      <c r="G647" t="inlineStr"/>
+      <c r="H647" t="inlineStr"/>
+      <c r="I647" t="inlineStr"/>
+      <c r="J647" t="inlineStr"/>
+      <c r="K647" t="inlineStr"/>
+      <c r="L647" t="inlineStr"/>
+      <c r="M647" t="inlineStr"/>
+      <c r="N647" t="inlineStr"/>
+      <c r="O647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                            Singular </t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr"/>
+      <c r="C648" t="inlineStr"/>
+      <c r="D648" t="inlineStr"/>
+      <c r="E648" t="inlineStr"/>
+      <c r="F648" t="inlineStr"/>
+      <c r="G648" t="inlineStr"/>
+      <c r="H648" t="inlineStr"/>
+      <c r="I648" t="inlineStr"/>
+      <c r="J648" t="inlineStr"/>
+      <c r="K648" t="inlineStr"/>
+      <c r="L648" t="inlineStr"/>
+      <c r="M648" t="inlineStr"/>
+      <c r="N648" t="inlineStr"/>
+      <c r="O648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom. /Voc.              periculum             danger (subj.  or pred.  nom. ) danger (d. a. </t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr"/>
+      <c r="C649" t="inlineStr"/>
+      <c r="D649" t="inlineStr"/>
+      <c r="E649" t="inlineStr"/>
+      <c r="F649" t="inlineStr"/>
+      <c r="G649" t="inlineStr"/>
+      <c r="H649" t="inlineStr"/>
+      <c r="I649" t="inlineStr"/>
+      <c r="J649" t="inlineStr"/>
+      <c r="K649" t="inlineStr"/>
+      <c r="L649" t="inlineStr"/>
+      <c r="M649" t="inlineStr"/>
+      <c r="N649" t="inlineStr"/>
+      <c r="O649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr"/>
+      <c r="B650" t="inlineStr"/>
+      <c r="C650" t="inlineStr"/>
+      <c r="D650" t="inlineStr"/>
+      <c r="E650" t="inlineStr"/>
+      <c r="F650" t="inlineStr"/>
+      <c r="G650" t="inlineStr"/>
+      <c r="H650" t="inlineStr"/>
+      <c r="I650" t="inlineStr"/>
+      <c r="J650" t="inlineStr"/>
+      <c r="K650" t="inlineStr"/>
+      <c r="L650" t="inlineStr"/>
+      <c r="M650" t="inlineStr"/>
+      <c r="N650" t="inlineStr"/>
+      <c r="O650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Gen.                      periculi                    of danger</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr"/>
+      <c r="C651" t="inlineStr"/>
+      <c r="D651" t="inlineStr"/>
+      <c r="E651" t="inlineStr"/>
+      <c r="F651" t="inlineStr"/>
+      <c r="G651" t="inlineStr"/>
+      <c r="H651" t="inlineStr"/>
+      <c r="I651" t="inlineStr"/>
+      <c r="J651" t="inlineStr"/>
+      <c r="K651" t="inlineStr"/>
+      <c r="L651" t="inlineStr"/>
+      <c r="M651" t="inlineStr"/>
+      <c r="N651" t="inlineStr"/>
+      <c r="O651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dat.                        periculo                     to danger/for danger </t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr"/>
+      <c r="C652" t="inlineStr"/>
+      <c r="D652" t="inlineStr"/>
+      <c r="E652" t="inlineStr"/>
+      <c r="F652" t="inlineStr"/>
+      <c r="G652" t="inlineStr"/>
+      <c r="H652" t="inlineStr"/>
+      <c r="I652" t="inlineStr"/>
+      <c r="J652" t="inlineStr"/>
+      <c r="K652" t="inlineStr"/>
+      <c r="L652" t="inlineStr"/>
+      <c r="M652" t="inlineStr"/>
+      <c r="N652" t="inlineStr"/>
+      <c r="O652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acc.                       periculum                danger (d. o. ) </t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr"/>
+      <c r="C653" t="inlineStr"/>
+      <c r="D653" t="inlineStr"/>
+      <c r="E653" t="inlineStr"/>
+      <c r="F653" t="inlineStr"/>
+      <c r="G653" t="inlineStr"/>
+      <c r="H653" t="inlineStr"/>
+      <c r="I653" t="inlineStr"/>
+      <c r="J653" t="inlineStr"/>
+      <c r="K653" t="inlineStr"/>
+      <c r="L653" t="inlineStr"/>
+      <c r="M653" t="inlineStr"/>
+      <c r="N653" t="inlineStr"/>
+      <c r="O653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Abl.                        periculo                     from danger; by/with danger; in danger</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr"/>
+      <c r="C654" t="inlineStr"/>
+      <c r="D654" t="inlineStr"/>
+      <c r="E654" t="inlineStr"/>
+      <c r="F654" t="inlineStr"/>
+      <c r="G654" t="inlineStr"/>
+      <c r="H654" t="inlineStr"/>
+      <c r="I654" t="inlineStr"/>
+      <c r="J654" t="inlineStr"/>
+      <c r="K654" t="inlineStr"/>
+      <c r="L654" t="inlineStr"/>
+      <c r="M654" t="inlineStr"/>
+      <c r="N654" t="inlineStr"/>
+      <c r="O654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                            Plural </t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr"/>
+      <c r="C655" t="inlineStr"/>
+      <c r="D655" t="inlineStr"/>
+      <c r="E655" t="inlineStr"/>
+      <c r="F655" t="inlineStr"/>
+      <c r="G655" t="inlineStr"/>
+      <c r="H655" t="inlineStr"/>
+      <c r="I655" t="inlineStr"/>
+      <c r="J655" t="inlineStr"/>
+      <c r="K655" t="inlineStr"/>
+      <c r="L655" t="inlineStr"/>
+      <c r="M655" t="inlineStr"/>
+      <c r="N655" t="inlineStr"/>
+      <c r="O655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nom. /Voc.           pericula                       dangers (subj.  or pred.  nom. ) </t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr"/>
+      <c r="C656" t="inlineStr"/>
+      <c r="D656" t="inlineStr"/>
+      <c r="E656" t="inlineStr"/>
+      <c r="F656" t="inlineStr"/>
+      <c r="G656" t="inlineStr"/>
+      <c r="H656" t="inlineStr"/>
+      <c r="I656" t="inlineStr"/>
+      <c r="J656" t="inlineStr"/>
+      <c r="K656" t="inlineStr"/>
+      <c r="L656" t="inlineStr"/>
+      <c r="M656" t="inlineStr"/>
+      <c r="N656" t="inlineStr"/>
+      <c r="O656" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                               dangers (d. a. </t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr"/>
+      <c r="C657" t="inlineStr"/>
+      <c r="D657" t="inlineStr"/>
+      <c r="E657" t="inlineStr"/>
+      <c r="F657" t="inlineStr"/>
+      <c r="G657" t="inlineStr"/>
+      <c r="H657" t="inlineStr"/>
+      <c r="I657" t="inlineStr"/>
+      <c r="J657" t="inlineStr"/>
+      <c r="K657" t="inlineStr"/>
+      <c r="L657" t="inlineStr"/>
+      <c r="M657" t="inlineStr"/>
+      <c r="N657" t="inlineStr"/>
+      <c r="O657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Gen.                     periculörum                of dangers</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr"/>
+      <c r="C658" t="inlineStr"/>
+      <c r="D658" t="inlineStr"/>
+      <c r="E658" t="inlineStr"/>
+      <c r="F658" t="inlineStr"/>
+      <c r="G658" t="inlineStr"/>
+      <c r="H658" t="inlineStr"/>
+      <c r="I658" t="inlineStr"/>
+      <c r="J658" t="inlineStr"/>
+      <c r="K658" t="inlineStr"/>
+      <c r="L658" t="inlineStr"/>
+      <c r="M658" t="inlineStr"/>
+      <c r="N658" t="inlineStr"/>
+      <c r="O658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Dat.                         periculis                   to dangers/for dangers</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr"/>
+      <c r="C659" t="inlineStr"/>
+      <c r="D659" t="inlineStr"/>
+      <c r="E659" t="inlineStr"/>
+      <c r="F659" t="inlineStr"/>
+      <c r="G659" t="inlineStr"/>
+      <c r="H659" t="inlineStr"/>
+      <c r="I659" t="inlineStr"/>
+      <c r="J659" t="inlineStr"/>
+      <c r="K659" t="inlineStr"/>
+      <c r="L659" t="inlineStr"/>
+      <c r="M659" t="inlineStr"/>
+      <c r="N659" t="inlineStr"/>
+      <c r="O659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acc.                        pericula                     dangers (d. o. ) </t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr"/>
+      <c r="C660" t="inlineStr"/>
+      <c r="D660" t="inlineStr"/>
+      <c r="E660" t="inlineStr"/>
+      <c r="F660" t="inlineStr"/>
+      <c r="G660" t="inlineStr"/>
+      <c r="H660" t="inlineStr"/>
+      <c r="I660" t="inlineStr"/>
+      <c r="J660" t="inlineStr"/>
+      <c r="K660" t="inlineStr"/>
+      <c r="L660" t="inlineStr"/>
+      <c r="M660" t="inlineStr"/>
+      <c r="N660" t="inlineStr"/>
+      <c r="O660" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Abl.                        periculis                   from dangers; by/with dangers; in dangers</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr"/>
+      <c r="C661" t="inlineStr"/>
+      <c r="D661" t="inlineStr"/>
+      <c r="E661" t="inlineStr"/>
+      <c r="F661" t="inlineStr"/>
+      <c r="G661" t="inlineStr"/>
+      <c r="H661" t="inlineStr"/>
+      <c r="I661" t="inlineStr"/>
+      <c r="J661" t="inlineStr"/>
+      <c r="K661" t="inlineStr"/>
+      <c r="L661" t="inlineStr"/>
+      <c r="M661" t="inlineStr"/>
+      <c r="N661" t="inlineStr"/>
+      <c r="O661" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OBSERVATIONS</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr"/>
+      <c r="C662" t="inlineStr"/>
+      <c r="D662" t="inlineStr"/>
+      <c r="E662" t="inlineStr"/>
+      <c r="F662" t="inlineStr"/>
+      <c r="G662" t="inlineStr"/>
+      <c r="H662" t="inlineStr"/>
+      <c r="I662" t="inlineStr"/>
+      <c r="J662" t="inlineStr"/>
+      <c r="K662" t="inlineStr"/>
+      <c r="L662" t="inlineStr"/>
+      <c r="M662" t="inlineStr"/>
+      <c r="N662" t="inlineStr"/>
+      <c r="O662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr"/>
+      <c r="C663" t="inlineStr"/>
+      <c r="D663" t="inlineStr"/>
+      <c r="E663" t="inlineStr"/>
+      <c r="F663" t="inlineStr"/>
+      <c r="G663" t="inlineStr"/>
+      <c r="H663" t="inlineStr"/>
+      <c r="I663" t="inlineStr"/>
+      <c r="J663" t="inlineStr"/>
+      <c r="K663" t="inlineStr"/>
+      <c r="L663" t="inlineStr"/>
+      <c r="M663" t="inlineStr"/>
+      <c r="N663" t="inlineStr"/>
+      <c r="O663" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Most of the endings for neuter nouns of the second declension are identical with the endings for masculine/feminine second-declension nouns. </t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr"/>
+      <c r="C664" t="inlineStr"/>
+      <c r="D664" t="inlineStr"/>
+      <c r="E664" t="inlineStr"/>
+      <c r="F664" t="inlineStr"/>
+      <c r="G664" t="inlineStr"/>
+      <c r="H664" t="inlineStr"/>
+      <c r="I664" t="inlineStr"/>
+      <c r="J664" t="inlineStr"/>
+      <c r="K664" t="inlineStr"/>
+      <c r="L664" t="inlineStr"/>
+      <c r="M664" t="inlineStr"/>
+      <c r="N664" t="inlineStr"/>
+      <c r="O664" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>1.大多数第二变格中性名词格尾与阳性/阴性名词一致</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr"/>
+      <c r="C665" t="inlineStr"/>
+      <c r="D665" t="inlineStr"/>
+      <c r="E665" t="inlineStr"/>
+      <c r="F665" t="inlineStr"/>
+      <c r="G665" t="inlineStr"/>
+      <c r="H665" t="inlineStr"/>
+      <c r="I665" t="inlineStr"/>
+      <c r="J665" t="inlineStr"/>
+      <c r="K665" t="inlineStr"/>
+      <c r="L665" t="inlineStr"/>
+      <c r="M665" t="inlineStr"/>
+      <c r="N665" t="inlineStr"/>
+      <c r="O665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Neuter nouns differ only in having -um in the nominative and vocative singular and -a in the nominative, vocative, and accusative plural. </t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr"/>
+      <c r="C666" t="inlineStr"/>
+      <c r="D666" t="inlineStr"/>
+      <c r="E666" t="inlineStr"/>
+      <c r="F666" t="inlineStr"/>
+      <c r="G666" t="inlineStr"/>
+      <c r="H666" t="inlineStr"/>
+      <c r="I666" t="inlineStr"/>
+      <c r="J666" t="inlineStr"/>
+      <c r="K666" t="inlineStr"/>
+      <c r="L666" t="inlineStr"/>
+      <c r="M666" t="inlineStr"/>
+      <c r="N666" t="inlineStr"/>
+      <c r="O666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>中性名词仅在主格、呼格单数（-um），主格、呼格、宾格复数（-a）上不同</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr"/>
+      <c r="C667" t="inlineStr"/>
+      <c r="D667" t="inlineStr"/>
+      <c r="E667" t="inlineStr"/>
+      <c r="F667" t="inlineStr"/>
+      <c r="G667" t="inlineStr"/>
+      <c r="H667" t="inlineStr"/>
+      <c r="I667" t="inlineStr"/>
+      <c r="J667" t="inlineStr"/>
+      <c r="K667" t="inlineStr"/>
+      <c r="L667" t="inlineStr"/>
+      <c r="M667" t="inlineStr"/>
+      <c r="N667" t="inlineStr"/>
+      <c r="O667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALL NEUTER WORDS IN LATIN HAVE IDENTICAL NOMINATIVE AND ACCUSATIVE FORMS IN BOTH THE SINGULAR AND THE PLURAL. </t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr"/>
+      <c r="C668" t="inlineStr"/>
+      <c r="D668" t="inlineStr"/>
+      <c r="E668" t="inlineStr"/>
+      <c r="F668" t="inlineStr"/>
+      <c r="G668" t="inlineStr"/>
+      <c r="H668" t="inlineStr"/>
+      <c r="I668" t="inlineStr"/>
+      <c r="J668" t="inlineStr"/>
+      <c r="K668" t="inlineStr"/>
+      <c r="L668" t="inlineStr"/>
+      <c r="M668" t="inlineStr"/>
+      <c r="N668" t="inlineStr"/>
+      <c r="O668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>谨记，每一个中性名词的主格与宾格单复数都一致</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr"/>
+      <c r="C669" t="inlineStr"/>
+      <c r="D669" t="inlineStr"/>
+      <c r="E669" t="inlineStr"/>
+      <c r="F669" t="inlineStr"/>
+      <c r="G669" t="inlineStr"/>
+      <c r="H669" t="inlineStr"/>
+      <c r="I669" t="inlineStr"/>
+      <c r="J669" t="inlineStr"/>
+      <c r="K669" t="inlineStr"/>
+      <c r="L669" t="inlineStr"/>
+      <c r="M669" t="inlineStr"/>
+      <c r="N669" t="inlineStr"/>
+      <c r="O669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr"/>
+      <c r="B670" t="inlineStr"/>
+      <c r="C670" t="inlineStr"/>
+      <c r="D670" t="inlineStr"/>
+      <c r="E670" t="inlineStr"/>
+      <c r="F670" t="inlineStr"/>
+      <c r="G670" t="inlineStr"/>
+      <c r="H670" t="inlineStr"/>
+      <c r="I670" t="inlineStr"/>
+      <c r="J670" t="inlineStr"/>
+      <c r="K670" t="inlineStr"/>
+      <c r="L670" t="inlineStr"/>
+      <c r="M670" t="inlineStr"/>
+      <c r="N670" t="inlineStr"/>
+      <c r="O670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2. As is true for masculine/feminine second-declension nouns, neuter nouns whose stems end in -i have two possible forms for the genitive singular, one a contraction of the other.  For example:</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr"/>
+      <c r="C671" t="inlineStr"/>
+      <c r="D671" t="inlineStr"/>
+      <c r="E671" t="inlineStr"/>
+      <c r="F671" t="inlineStr"/>
+      <c r="G671" t="inlineStr"/>
+      <c r="H671" t="inlineStr"/>
+      <c r="I671" t="inlineStr"/>
+      <c r="J671" t="inlineStr"/>
+      <c r="K671" t="inlineStr"/>
+      <c r="L671" t="inlineStr"/>
+      <c r="M671" t="inlineStr"/>
+      <c r="N671" t="inlineStr"/>
+      <c r="O671" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2.和第二变格阳性/阴性名词一样，词干以-i结尾的中性名词有两种属格单数形式，其一是另一的缩约形式。例如：</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr"/>
+      <c r="C672" t="inlineStr"/>
+      <c r="D672" t="inlineStr"/>
+      <c r="E672" t="inlineStr"/>
+      <c r="F672" t="inlineStr"/>
+      <c r="G672" t="inlineStr"/>
+      <c r="H672" t="inlineStr"/>
+      <c r="I672" t="inlineStr"/>
+      <c r="J672" t="inlineStr"/>
+      <c r="K672" t="inlineStr"/>
+      <c r="L672" t="inlineStr"/>
+      <c r="M672" t="inlineStr"/>
+      <c r="N672" t="inlineStr"/>
+      <c r="O672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               consilium, consilii or consili n.  plan, advice; judgment </t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr"/>
+      <c r="C673" t="inlineStr"/>
+      <c r="D673" t="inlineStr"/>
+      <c r="E673" t="inlineStr"/>
+      <c r="F673" t="inlineStr"/>
+      <c r="G673" t="inlineStr"/>
+      <c r="H673" t="inlineStr"/>
+      <c r="I673" t="inlineStr"/>
+      <c r="J673" t="inlineStr"/>
+      <c r="K673" t="inlineStr"/>
+      <c r="L673" t="inlineStr"/>
+      <c r="M673" t="inlineStr"/>
+      <c r="N673" t="inlineStr"/>
+      <c r="O673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>consilium, consilii 或 consili 中（计划，建议；决定）</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr"/>
+      <c r="C674" t="inlineStr"/>
+      <c r="D674" t="inlineStr"/>
+      <c r="E674" t="inlineStr"/>
+      <c r="F674" t="inlineStr"/>
+      <c r="G674" t="inlineStr"/>
+      <c r="H674" t="inlineStr"/>
+      <c r="I674" t="inlineStr"/>
+      <c r="J674" t="inlineStr"/>
+      <c r="K674" t="inlineStr"/>
+      <c r="L674" t="inlineStr"/>
+      <c r="M674" t="inlineStr"/>
+      <c r="N674" t="inlineStr"/>
+      <c r="O674" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>• DRILL 4, PAGE 15, MAY NOW BE DONE</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr"/>
+      <c r="C675" t="inlineStr"/>
+      <c r="D675" t="inlineStr"/>
+      <c r="E675" t="inlineStr"/>
+      <c r="F675" t="inlineStr"/>
+      <c r="G675" t="inlineStr"/>
+      <c r="H675" t="inlineStr"/>
+      <c r="I675" t="inlineStr"/>
+      <c r="J675" t="inlineStr"/>
+      <c r="K675" t="inlineStr"/>
+      <c r="L675" t="inlineStr"/>
+      <c r="M675" t="inlineStr"/>
+      <c r="N675" t="inlineStr"/>
+      <c r="O675" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>略</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr"/>
+      <c r="C676" t="inlineStr"/>
+      <c r="D676" t="inlineStr"/>
+      <c r="E676" t="inlineStr"/>
+      <c r="F676" t="inlineStr"/>
+      <c r="G676" t="inlineStr"/>
+      <c r="H676" t="inlineStr"/>
+      <c r="I676" t="inlineStr"/>
+      <c r="J676" t="inlineStr"/>
+      <c r="K676" t="inlineStr"/>
+      <c r="L676" t="inlineStr"/>
+      <c r="M676" t="inlineStr"/>
+      <c r="N676" t="inlineStr"/>
+      <c r="O676" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr"/>
+      <c r="B677" t="inlineStr"/>
+      <c r="C677" t="inlineStr"/>
+      <c r="D677" t="inlineStr"/>
+      <c r="E677" t="inlineStr"/>
+      <c r="F677" t="inlineStr"/>
+      <c r="G677" t="inlineStr"/>
+      <c r="H677" t="inlineStr"/>
+      <c r="I677" t="inlineStr"/>
+      <c r="J677" t="inlineStr"/>
+      <c r="K677" t="inlineStr"/>
+      <c r="L677" t="inlineStr"/>
+      <c r="M677" t="inlineStr"/>
+      <c r="N677" t="inlineStr"/>
+      <c r="O677" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>序号56，页数24（空白页）</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr"/>
+      <c r="C678" t="inlineStr"/>
+      <c r="D678" t="inlineStr"/>
+      <c r="E678" t="inlineStr"/>
+      <c r="F678" t="inlineStr"/>
+      <c r="G678" t="inlineStr"/>
+      <c r="H678" t="inlineStr"/>
+      <c r="I678" t="inlineStr"/>
+      <c r="J678" t="inlineStr"/>
+      <c r="K678" t="inlineStr"/>
+      <c r="L678" t="inlineStr"/>
+      <c r="M678" t="inlineStr"/>
+      <c r="N678" t="inlineStr"/>
+      <c r="O678" t="inlineStr"/>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>你在期待什么？猜猜这页为什么叫空白页？（手动滑稽）</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr"/>
+      <c r="C679" t="inlineStr"/>
+      <c r="D679" t="inlineStr"/>
+      <c r="E679" t="inlineStr"/>
+      <c r="F679" t="inlineStr"/>
+      <c r="G679" t="inlineStr"/>
+      <c r="H679" t="inlineStr"/>
+      <c r="I679" t="inlineStr"/>
+      <c r="J679" t="inlineStr"/>
+      <c r="K679" t="inlineStr"/>
+      <c r="L679" t="inlineStr"/>
+      <c r="M679" t="inlineStr"/>
+      <c r="N679" t="inlineStr"/>
+      <c r="O679" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
